--- a/dataset/dewasa.xlsx
+++ b/dataset/dewasa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbokprom12021/PycharmProjects/CKG-Helper/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD195EB-3BD8-9D4C-BB70-6CE72C92F755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA62621-C57C-174C-868E-3FC8D4E5B358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3674,7 +3674,7 @@
       <c r="FT4" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="47">
+  <dataValidations count="48">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E4" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Belum Menikah,Menikah,Cerai Mati,Cerai Hidup"</formula1>
     </dataValidation>
@@ -3684,7 +3684,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H4" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Non disabilitas,Penyandang disabilitas"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 AG2:AG4 BY2:BY4 CJ2:CJ4 FH2:FH4 FK2:FK4" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K4 AG2:AG4 BY2:BY4 FK2:FK4 FH2:FH4 CJ4" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:Y4" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Tidak sama sekali,Kurang dari 1 minggu,Lebih dari 1 minggu,Hampir setiap hari"</formula1>
     </dataValidation>
@@ -3813,6 +3813,16 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EU2:EU4" xr:uid="{00000000-0002-0000-0000-00002E000000}">
       <formula1>"Normal,Curiga kanker"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ2 CJ3" xr:uid="{48CEE897-889E-1A47-8D8A-CBB17E8BB85E}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>Mtb not detected (Neg),"Mtb detected, Rif resistance not detected (Rif Sen)","Mtb detected, Rif resistance detected (Rif Res)","MTB detected, Rif Resistance Indeterminate (Rif Indet)",Invalid,Error,No Result</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"Mtb not detected (Neg),Mtb detected, Rif resistance not detected (Rif Sen),Mtb detected, Rif resistance detected (Rif Res),MTB detected, Rif Resistance Indeterminate (Rif Indet),Invalid,Error,No Result"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset/dewasa.xlsx
+++ b/dataset/dewasa.xlsx
@@ -2605,10 +2605,7 @@
       </c>
       <c r="FU2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED: Locator.click: Target page, context or browser has been closed
-Call log:
-  - waiting for locator("div.cursor-pointer.px-3").filter(has_text="Sedang Pemeriksaan")
-</t>
+          <t>FAILED: Pasien tidak ditemukan pada semua status pemeriksaan.</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3441,7 @@
       </c>
       <c r="FU3" t="inlineStr">
         <is>
-          <t>FAILED: Page.goto: Target page, context or browser has been closed</t>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3584,7 @@
       <c r="FT4" s="2" t="n"/>
       <c r="FU4" t="inlineStr">
         <is>
-          <t>FAILED: Page.goto: Target page, context or browser has been closed</t>
+          <t>FAILED: Pasien tidak ditemukan pada semua status pemeriksaan.</t>
         </is>
       </c>
     </row>

--- a/dataset/dewasa.xlsx
+++ b/dataset/dewasa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbokprom12021/PycharmProjects/CKG-Helper/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57EA6D0A-5A91-324E-8B8B-5359178134FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9058D131A42A90127D7C0170EC8C098B8BD8573F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="-21000" windowWidth="36000" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -708,7 +708,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="358">
   <si>
     <t>batas_awal</t>
   </si>
@@ -1373,6 +1373,9 @@
     <t>Non Reaktif</t>
   </si>
   <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
     <t>ADI RUKMINI</t>
   </si>
   <si>
@@ -1412,7 +1415,10 @@
     <t>65</t>
   </si>
   <si>
-    <t>198</t>
+    <t>76</t>
+  </si>
+  <si>
+    <t>156</t>
   </si>
   <si>
     <t>Anti HCV Non Reaktif</t>
@@ -1449,6 +1455,333 @@
   </si>
   <si>
     <t>Memiliki lingkungan dalam rumah yang sehat</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>Siti Nurhamida</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Tidak ada</t>
+  </si>
+  <si>
+    <t>Tidak dilakukan</t>
+  </si>
+  <si>
+    <t>Normal (visus 6/6 - 6/12)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Alifa Wulandari</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Amalia</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Farah Andriani</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>0,9</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Siti Andayani</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>0,10</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Ary Widjajanti</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Masyudi</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Dwi Usriya</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>Ibnu Haris</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>187</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Fitri Ayu Nurjannatin</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>Maya Sukma Indah Refiana</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>Untung Slamet Setiawan</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Rofiqa Yuni Astuti</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Yuni Retnowati</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Cahyo Murtanto</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>0,20</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
 </sst>
 </file>
@@ -1824,8 +2157,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EX4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:EX19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -2873,6 +3206,9 @@
       <c r="EW2" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="EX2" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="3" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -2882,7 +3218,7 @@
         <v>155</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
         <v>157</v>
@@ -3326,19 +3662,22 @@
       <c r="EW3" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="EX3" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="4" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>158</v>
@@ -3485,22 +3824,22 @@
         <v>20</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="BG4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="BH4" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="BI4" s="2" t="s">
         <v>158</v>
       </c>
       <c r="BJ4" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="BK4" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="BL4" s="2"/>
       <c r="BM4" s="2"/>
@@ -3510,7 +3849,7 @@
       </c>
       <c r="BP4" s="2"/>
       <c r="BQ4" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BR4" s="2" t="s">
         <v>168</v>
@@ -3560,7 +3899,7 @@
         <v>182</v>
       </c>
       <c r="CI4" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="CJ4" s="2" t="s">
         <v>182</v>
@@ -3625,16 +3964,16 @@
       </c>
       <c r="DE4" s="2"/>
       <c r="DF4" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="DG4" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="DH4" s="2" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="DI4" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="DJ4" s="2" t="s">
         <v>197</v>
@@ -3646,22 +3985,22 @@
         <v>199</v>
       </c>
       <c r="DM4" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="DN4" s="2" t="s">
         <v>201</v>
       </c>
       <c r="DO4" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="DP4" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="DQ4" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="DR4" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="DS4" s="2" t="s">
         <v>203</v>
@@ -3679,7 +4018,7 @@
         <v>173</v>
       </c>
       <c r="DX4" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="DY4" s="2" t="s">
         <v>158</v>
@@ -3709,28 +4048,28 @@
         <v>210</v>
       </c>
       <c r="EH4" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="EI4" s="2" t="s">
         <v>208</v>
       </c>
       <c r="EJ4" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="EK4" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="EL4" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="EM4" s="2" t="s">
         <v>215</v>
       </c>
       <c r="EN4" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="EO4" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="EP4" s="2" t="s">
         <v>218</v>
@@ -3755,156 +4094,6654 @@
       </c>
       <c r="EW4" s="2" t="s">
         <v>220</v>
+      </c>
+      <c r="EX4" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K5" t="s">
+        <v>158</v>
+      </c>
+      <c r="L5" t="s">
+        <v>158</v>
+      </c>
+      <c r="M5" t="s">
+        <v>158</v>
+      </c>
+      <c r="N5" t="s">
+        <v>158</v>
+      </c>
+      <c r="O5" t="s">
+        <v>158</v>
+      </c>
+      <c r="P5" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>158</v>
+      </c>
+      <c r="R5" t="s">
+        <v>158</v>
+      </c>
+      <c r="S5" t="s">
+        <v>158</v>
+      </c>
+      <c r="T5" t="s">
+        <v>158</v>
+      </c>
+      <c r="U5" t="s">
+        <v>162</v>
+      </c>
+      <c r="V5" t="s">
+        <v>162</v>
+      </c>
+      <c r="W5" t="s">
+        <v>162</v>
+      </c>
+      <c r="X5" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO5">
+        <v>5</v>
+      </c>
+      <c r="AP5">
+        <v>30</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR5">
+        <v>6</v>
+      </c>
+      <c r="AS5">
+        <v>30</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU5">
+        <v>3</v>
+      </c>
+      <c r="AV5">
+        <v>60</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX5">
+        <v>2</v>
+      </c>
+      <c r="AY5">
+        <v>100</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA5">
+        <v>1</v>
+      </c>
+      <c r="BB5">
+        <v>20</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD5">
+        <v>1</v>
+      </c>
+      <c r="BE5">
+        <v>20</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="BL5" s="2"/>
+      <c r="BM5" s="2"/>
+      <c r="BN5" s="2"/>
+      <c r="BO5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP5" s="2"/>
+      <c r="BQ5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS5" s="2"/>
+      <c r="BT5" s="2"/>
+      <c r="BU5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD5" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="CE5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI5" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ5" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ5" s="2"/>
+      <c r="DA5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE5" s="2"/>
+      <c r="DF5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DG5" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH5" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="DI5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DJ5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM5" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN5" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="DP5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR5" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK5" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL5" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN5" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER5" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="ES5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV5" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX5" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" t="s">
+        <v>158</v>
+      </c>
+      <c r="J6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K6" t="s">
+        <v>158</v>
+      </c>
+      <c r="L6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M6" t="s">
+        <v>158</v>
+      </c>
+      <c r="N6" t="s">
+        <v>158</v>
+      </c>
+      <c r="O6" t="s">
+        <v>158</v>
+      </c>
+      <c r="P6" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>158</v>
+      </c>
+      <c r="R6" t="s">
+        <v>158</v>
+      </c>
+      <c r="S6" t="s">
+        <v>158</v>
+      </c>
+      <c r="T6" t="s">
+        <v>158</v>
+      </c>
+      <c r="U6" t="s">
+        <v>162</v>
+      </c>
+      <c r="V6" t="s">
+        <v>162</v>
+      </c>
+      <c r="W6" t="s">
+        <v>162</v>
+      </c>
+      <c r="X6" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO6">
+        <v>5</v>
+      </c>
+      <c r="AP6">
+        <v>60</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR6">
+        <v>6</v>
+      </c>
+      <c r="AS6">
+        <v>30</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU6">
+        <v>3</v>
+      </c>
+      <c r="AV6">
+        <v>120</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX6">
+        <v>2</v>
+      </c>
+      <c r="AY6">
+        <v>60</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA6">
+        <v>1</v>
+      </c>
+      <c r="BB6">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD6">
+        <v>1</v>
+      </c>
+      <c r="BE6">
+        <v>20</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="BL6" s="2"/>
+      <c r="BM6" s="2"/>
+      <c r="BN6" s="2"/>
+      <c r="BO6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP6" s="2"/>
+      <c r="BQ6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BS6" s="2"/>
+      <c r="BT6" s="2"/>
+      <c r="BU6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC6" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP6" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ6" s="2"/>
+      <c r="DA6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE6" s="2"/>
+      <c r="DF6" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH6" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="DI6" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="DJ6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM6" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO6" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="DP6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS6" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU6" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG6" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH6" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ6" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK6" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL6" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN6" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO6" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER6" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="ES6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX6" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" t="s">
+        <v>161</v>
+      </c>
+      <c r="K7" t="s">
+        <v>158</v>
+      </c>
+      <c r="L7" t="s">
+        <v>158</v>
+      </c>
+      <c r="M7" t="s">
+        <v>158</v>
+      </c>
+      <c r="N7" t="s">
+        <v>158</v>
+      </c>
+      <c r="O7" t="s">
+        <v>158</v>
+      </c>
+      <c r="P7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>158</v>
+      </c>
+      <c r="R7" t="s">
+        <v>158</v>
+      </c>
+      <c r="S7" t="s">
+        <v>158</v>
+      </c>
+      <c r="T7" t="s">
+        <v>158</v>
+      </c>
+      <c r="U7" t="s">
+        <v>162</v>
+      </c>
+      <c r="V7" t="s">
+        <v>162</v>
+      </c>
+      <c r="W7" t="s">
+        <v>162</v>
+      </c>
+      <c r="X7" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO7">
+        <v>5</v>
+      </c>
+      <c r="AP7">
+        <v>60</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR7">
+        <v>6</v>
+      </c>
+      <c r="AS7">
+        <v>30</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU7">
+        <v>3</v>
+      </c>
+      <c r="AV7">
+        <v>90</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX7">
+        <v>2</v>
+      </c>
+      <c r="AY7">
+        <v>25</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA7">
+        <v>1</v>
+      </c>
+      <c r="BB7">
+        <v>20</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD7">
+        <v>1</v>
+      </c>
+      <c r="BE7">
+        <v>20</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="BL7" s="2"/>
+      <c r="BM7" s="2"/>
+      <c r="BN7" s="2"/>
+      <c r="BO7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP7" s="2"/>
+      <c r="BQ7" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS7" s="2"/>
+      <c r="BT7" s="2"/>
+      <c r="BU7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC7" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI7" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK7" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM7" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO7" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP7" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ7" s="2"/>
+      <c r="DA7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE7" s="2"/>
+      <c r="DF7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="DG7" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH7" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="DI7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="DJ7" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO7" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="DP7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH7" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ7" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL7" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN7" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="ES7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX7" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" t="s">
+        <v>161</v>
+      </c>
+      <c r="K8" t="s">
+        <v>158</v>
+      </c>
+      <c r="L8" t="s">
+        <v>158</v>
+      </c>
+      <c r="M8" t="s">
+        <v>158</v>
+      </c>
+      <c r="N8" t="s">
+        <v>158</v>
+      </c>
+      <c r="O8" t="s">
+        <v>158</v>
+      </c>
+      <c r="P8" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>158</v>
+      </c>
+      <c r="R8" t="s">
+        <v>158</v>
+      </c>
+      <c r="S8" t="s">
+        <v>158</v>
+      </c>
+      <c r="T8" t="s">
+        <v>158</v>
+      </c>
+      <c r="U8" t="s">
+        <v>162</v>
+      </c>
+      <c r="V8" t="s">
+        <v>162</v>
+      </c>
+      <c r="W8" t="s">
+        <v>162</v>
+      </c>
+      <c r="X8" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO8">
+        <v>5</v>
+      </c>
+      <c r="AP8">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR8">
+        <v>6</v>
+      </c>
+      <c r="AS8">
+        <v>30</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU8">
+        <v>3</v>
+      </c>
+      <c r="AV8">
+        <v>120</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX8">
+        <v>2</v>
+      </c>
+      <c r="AY8">
+        <v>100</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>20</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD8">
+        <v>1</v>
+      </c>
+      <c r="BE8">
+        <v>20</v>
+      </c>
+      <c r="BF8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="BG8" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="BH8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK8" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="BL8" s="2"/>
+      <c r="BM8" s="2"/>
+      <c r="BN8" s="2"/>
+      <c r="BO8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP8" s="2"/>
+      <c r="BQ8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BR8" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BS8" s="2"/>
+      <c r="BT8" s="2"/>
+      <c r="BU8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI8" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN8" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR8" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ8" s="2"/>
+      <c r="DA8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE8" s="2"/>
+      <c r="DF8" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG8" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="DI8" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="DJ8" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL8" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM8" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO8" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="DP8" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ8" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS8" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER8" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="ES8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX8" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="9" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" t="s">
+        <v>158</v>
+      </c>
+      <c r="J9" t="s">
+        <v>161</v>
+      </c>
+      <c r="K9" t="s">
+        <v>158</v>
+      </c>
+      <c r="L9" t="s">
+        <v>158</v>
+      </c>
+      <c r="M9" t="s">
+        <v>158</v>
+      </c>
+      <c r="N9" t="s">
+        <v>158</v>
+      </c>
+      <c r="O9" t="s">
+        <v>158</v>
+      </c>
+      <c r="P9" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>158</v>
+      </c>
+      <c r="R9" t="s">
+        <v>158</v>
+      </c>
+      <c r="S9" t="s">
+        <v>158</v>
+      </c>
+      <c r="T9" t="s">
+        <v>158</v>
+      </c>
+      <c r="U9" t="s">
+        <v>162</v>
+      </c>
+      <c r="V9" t="s">
+        <v>162</v>
+      </c>
+      <c r="W9" t="s">
+        <v>162</v>
+      </c>
+      <c r="X9" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO9">
+        <v>3</v>
+      </c>
+      <c r="AP9">
+        <v>60</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR9">
+        <v>6</v>
+      </c>
+      <c r="AS9">
+        <v>30</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>60</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX9">
+        <v>2</v>
+      </c>
+      <c r="AY9">
+        <v>30</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA9">
+        <v>1</v>
+      </c>
+      <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD9">
+        <v>1</v>
+      </c>
+      <c r="BE9">
+        <v>20</v>
+      </c>
+      <c r="BF9" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="BG9" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BH9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="BI9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ9" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK9" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="BL9" s="2"/>
+      <c r="BM9" s="2"/>
+      <c r="BN9" s="2"/>
+      <c r="BO9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP9" s="2"/>
+      <c r="BQ9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="BR9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BS9" s="2"/>
+      <c r="BT9" s="2"/>
+      <c r="BU9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB9" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ9" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK9" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL9" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM9" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO9" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP9" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ9" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR9" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ9" s="2"/>
+      <c r="DA9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE9" s="2"/>
+      <c r="DF9" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="DG9" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH9" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="DI9" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="DJ9" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL9" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM9" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO9" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="DP9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ9" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU9" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX9" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED9" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG9" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH9" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI9" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ9" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK9" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL9" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN9" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER9" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="ES9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX9" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C10" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K10" t="s">
+        <v>158</v>
+      </c>
+      <c r="L10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M10" t="s">
+        <v>158</v>
+      </c>
+      <c r="N10" t="s">
+        <v>158</v>
+      </c>
+      <c r="O10" t="s">
+        <v>158</v>
+      </c>
+      <c r="P10" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>158</v>
+      </c>
+      <c r="R10" t="s">
+        <v>158</v>
+      </c>
+      <c r="S10" t="s">
+        <v>158</v>
+      </c>
+      <c r="T10" t="s">
+        <v>158</v>
+      </c>
+      <c r="U10" t="s">
+        <v>162</v>
+      </c>
+      <c r="V10" t="s">
+        <v>162</v>
+      </c>
+      <c r="W10" t="s">
+        <v>162</v>
+      </c>
+      <c r="X10" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO10">
+        <v>5</v>
+      </c>
+      <c r="AP10">
+        <v>60</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR10">
+        <v>6</v>
+      </c>
+      <c r="AS10">
+        <v>30</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU10">
+        <v>3</v>
+      </c>
+      <c r="AV10">
+        <v>120</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX10">
+        <v>2</v>
+      </c>
+      <c r="AY10">
+        <v>35</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA10">
+        <v>1</v>
+      </c>
+      <c r="BB10">
+        <v>20</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD10">
+        <v>1</v>
+      </c>
+      <c r="BE10">
+        <v>20</v>
+      </c>
+      <c r="BF10" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="BG10" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BH10" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="BI10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK10" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="BL10" s="2"/>
+      <c r="BM10" s="2"/>
+      <c r="BN10" s="2"/>
+      <c r="BO10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP10" s="2"/>
+      <c r="BQ10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BR10" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BS10" s="2"/>
+      <c r="BT10" s="2"/>
+      <c r="BU10" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB10" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE10" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI10" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ10" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK10" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM10" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN10" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO10" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP10" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ10" s="2"/>
+      <c r="DA10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE10" s="2"/>
+      <c r="DF10" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG10" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH10" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="DI10" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="DJ10" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM10" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="DP10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ10" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR10" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU10" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG10" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH10" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ10" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK10" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP10" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER10" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="ES10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX10" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" t="s">
+        <v>160</v>
+      </c>
+      <c r="I11" t="s">
+        <v>158</v>
+      </c>
+      <c r="J11" t="s">
+        <v>161</v>
+      </c>
+      <c r="K11" t="s">
+        <v>158</v>
+      </c>
+      <c r="L11" t="s">
+        <v>158</v>
+      </c>
+      <c r="M11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N11" t="s">
+        <v>158</v>
+      </c>
+      <c r="O11" t="s">
+        <v>158</v>
+      </c>
+      <c r="P11" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>158</v>
+      </c>
+      <c r="R11" t="s">
+        <v>158</v>
+      </c>
+      <c r="S11" t="s">
+        <v>158</v>
+      </c>
+      <c r="T11" t="s">
+        <v>158</v>
+      </c>
+      <c r="U11" t="s">
+        <v>162</v>
+      </c>
+      <c r="V11" t="s">
+        <v>162</v>
+      </c>
+      <c r="W11" t="s">
+        <v>162</v>
+      </c>
+      <c r="X11" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO11">
+        <v>5</v>
+      </c>
+      <c r="AP11">
+        <v>60</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR11">
+        <v>6</v>
+      </c>
+      <c r="AS11">
+        <v>30</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU11">
+        <v>3</v>
+      </c>
+      <c r="AV11">
+        <v>100</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX11">
+        <v>2</v>
+      </c>
+      <c r="AY11">
+        <v>35</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA11">
+        <v>1</v>
+      </c>
+      <c r="BB11">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD11">
+        <v>1</v>
+      </c>
+      <c r="BE11">
+        <v>20</v>
+      </c>
+      <c r="BF11" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="BG11" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="BH11" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="BI11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK11" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="BL11" s="2"/>
+      <c r="BM11" s="2"/>
+      <c r="BN11" s="2"/>
+      <c r="BO11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP11" s="2"/>
+      <c r="BQ11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="BR11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS11" s="2"/>
+      <c r="BT11" s="2"/>
+      <c r="BU11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD11" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE11" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK11" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL11" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM11" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN11" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO11" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP11" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ11" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ11" s="2"/>
+      <c r="DA11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE11" s="2"/>
+      <c r="DF11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH11" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="DI11" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="DJ11" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL11" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM11" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="DP11" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ11" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR11" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX11" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH11" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ11" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK11" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL11" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN11" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER11" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="ES11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX11" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="s">
+        <v>309</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" t="s">
+        <v>160</v>
+      </c>
+      <c r="I12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J12" t="s">
+        <v>161</v>
+      </c>
+      <c r="K12" t="s">
+        <v>158</v>
+      </c>
+      <c r="L12" t="s">
+        <v>158</v>
+      </c>
+      <c r="M12" t="s">
+        <v>158</v>
+      </c>
+      <c r="N12" t="s">
+        <v>158</v>
+      </c>
+      <c r="O12" t="s">
+        <v>158</v>
+      </c>
+      <c r="P12" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>158</v>
+      </c>
+      <c r="R12" t="s">
+        <v>158</v>
+      </c>
+      <c r="S12" t="s">
+        <v>158</v>
+      </c>
+      <c r="T12" t="s">
+        <v>158</v>
+      </c>
+      <c r="U12" t="s">
+        <v>162</v>
+      </c>
+      <c r="V12" t="s">
+        <v>162</v>
+      </c>
+      <c r="W12" t="s">
+        <v>162</v>
+      </c>
+      <c r="X12" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO12">
+        <v>5</v>
+      </c>
+      <c r="AP12">
+        <v>60</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR12">
+        <v>6</v>
+      </c>
+      <c r="AS12">
+        <v>30</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU12">
+        <v>3</v>
+      </c>
+      <c r="AV12">
+        <v>60</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX12">
+        <v>2</v>
+      </c>
+      <c r="AY12">
+        <v>100</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA12">
+        <v>1</v>
+      </c>
+      <c r="BB12">
+        <v>20</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <v>20</v>
+      </c>
+      <c r="BF12" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BG12" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="BH12" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="BI12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK12" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="BL12" s="2"/>
+      <c r="BM12" s="2"/>
+      <c r="BN12" s="2"/>
+      <c r="BO12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP12" s="2"/>
+      <c r="BQ12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="BR12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BS12" s="2"/>
+      <c r="BT12" s="2"/>
+      <c r="BU12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD12" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK12" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN12" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ12" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ12" s="2"/>
+      <c r="DA12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE12" s="2"/>
+      <c r="DF12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH12" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="DI12" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="DJ12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO12" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="DP12" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ12" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB12" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED12" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG12" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI12" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK12" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL12" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN12" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO12" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="ES12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV12" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX12" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" t="s">
+        <v>316</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J13" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" t="s">
+        <v>158</v>
+      </c>
+      <c r="L13" t="s">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s">
+        <v>158</v>
+      </c>
+      <c r="N13" t="s">
+        <v>158</v>
+      </c>
+      <c r="O13" t="s">
+        <v>158</v>
+      </c>
+      <c r="P13" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>158</v>
+      </c>
+      <c r="R13" t="s">
+        <v>158</v>
+      </c>
+      <c r="S13" t="s">
+        <v>158</v>
+      </c>
+      <c r="T13" t="s">
+        <v>158</v>
+      </c>
+      <c r="U13" t="s">
+        <v>162</v>
+      </c>
+      <c r="V13" t="s">
+        <v>162</v>
+      </c>
+      <c r="W13" t="s">
+        <v>162</v>
+      </c>
+      <c r="X13" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO13">
+        <v>3</v>
+      </c>
+      <c r="AP13">
+        <v>60</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR13">
+        <v>6</v>
+      </c>
+      <c r="AS13">
+        <v>30</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU13">
+        <v>3</v>
+      </c>
+      <c r="AV13">
+        <v>120</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX13">
+        <v>2</v>
+      </c>
+      <c r="AY13">
+        <v>45</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA13">
+        <v>1</v>
+      </c>
+      <c r="BB13">
+        <v>20</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BE13">
+        <v>20</v>
+      </c>
+      <c r="BF13" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="BG13" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="BH13" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="BI13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK13" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="BL13" s="2"/>
+      <c r="BM13" s="2"/>
+      <c r="BN13" s="2"/>
+      <c r="BO13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP13" s="2"/>
+      <c r="BQ13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BR13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS13" s="2"/>
+      <c r="BT13" s="2"/>
+      <c r="BU13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM13" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ13" s="2"/>
+      <c r="DA13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE13" s="2"/>
+      <c r="DF13" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="DG13" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH13" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="DI13" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="DJ13" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL13" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM13" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO13" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="DP13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ13" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR13" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT13" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX13" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG13" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK13" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL13" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN13" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO13" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER13" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="ES13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX13" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" t="s">
+        <v>323</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" t="s">
+        <v>161</v>
+      </c>
+      <c r="K14" t="s">
+        <v>158</v>
+      </c>
+      <c r="L14" t="s">
+        <v>158</v>
+      </c>
+      <c r="M14" t="s">
+        <v>158</v>
+      </c>
+      <c r="N14" t="s">
+        <v>158</v>
+      </c>
+      <c r="O14" t="s">
+        <v>158</v>
+      </c>
+      <c r="P14" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>158</v>
+      </c>
+      <c r="R14" t="s">
+        <v>158</v>
+      </c>
+      <c r="S14" t="s">
+        <v>158</v>
+      </c>
+      <c r="T14" t="s">
+        <v>158</v>
+      </c>
+      <c r="U14" t="s">
+        <v>162</v>
+      </c>
+      <c r="V14" t="s">
+        <v>162</v>
+      </c>
+      <c r="W14" t="s">
+        <v>162</v>
+      </c>
+      <c r="X14" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO14">
+        <v>5</v>
+      </c>
+      <c r="AP14">
+        <v>45</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR14">
+        <v>6</v>
+      </c>
+      <c r="AS14">
+        <v>30</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU14">
+        <v>3</v>
+      </c>
+      <c r="AV14">
+        <v>30</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX14">
+        <v>2</v>
+      </c>
+      <c r="AY14">
+        <v>60</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA14">
+        <v>1</v>
+      </c>
+      <c r="BB14">
+        <v>20</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD14">
+        <v>1</v>
+      </c>
+      <c r="BE14">
+        <v>20</v>
+      </c>
+      <c r="BF14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="BG14" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="BH14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ14" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK14" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="BL14" s="2"/>
+      <c r="BM14" s="2"/>
+      <c r="BN14" s="2"/>
+      <c r="BO14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP14" s="2"/>
+      <c r="BQ14" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="BR14" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS14" s="2"/>
+      <c r="BT14" s="2"/>
+      <c r="BU14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC14" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD14" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE14" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI14" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK14" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM14" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN14" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ14" s="2"/>
+      <c r="DA14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE14" s="2"/>
+      <c r="DF14" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="DI14" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="DJ14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK14" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM14" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="DP14" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR14" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS14" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG14" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ14" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL14" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM14" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN14" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER14" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="ES14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX14" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" t="s">
+        <v>328</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K15" t="s">
+        <v>158</v>
+      </c>
+      <c r="L15" t="s">
+        <v>158</v>
+      </c>
+      <c r="M15" t="s">
+        <v>158</v>
+      </c>
+      <c r="N15" t="s">
+        <v>158</v>
+      </c>
+      <c r="O15" t="s">
+        <v>158</v>
+      </c>
+      <c r="P15" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>158</v>
+      </c>
+      <c r="R15" t="s">
+        <v>158</v>
+      </c>
+      <c r="S15" t="s">
+        <v>158</v>
+      </c>
+      <c r="T15" t="s">
+        <v>158</v>
+      </c>
+      <c r="U15" t="s">
+        <v>162</v>
+      </c>
+      <c r="V15" t="s">
+        <v>162</v>
+      </c>
+      <c r="W15" t="s">
+        <v>162</v>
+      </c>
+      <c r="X15" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO15">
+        <v>2</v>
+      </c>
+      <c r="AP15">
+        <v>60</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR15">
+        <v>6</v>
+      </c>
+      <c r="AS15">
+        <v>30</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU15">
+        <v>3</v>
+      </c>
+      <c r="AV15">
+        <v>120</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX15">
+        <v>2</v>
+      </c>
+      <c r="AY15">
+        <v>100</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA15">
+        <v>1</v>
+      </c>
+      <c r="BB15">
+        <v>20</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BE15">
+        <v>20</v>
+      </c>
+      <c r="BF15" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="BG15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="BH15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="BI15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="BL15" s="2"/>
+      <c r="BM15" s="2"/>
+      <c r="BN15" s="2"/>
+      <c r="BO15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP15" s="2"/>
+      <c r="BQ15" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="BR15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS15" s="2"/>
+      <c r="BT15" s="2"/>
+      <c r="BU15" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK15" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL15" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN15" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ15" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR15" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU15" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ15" s="2"/>
+      <c r="DA15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE15" s="2"/>
+      <c r="DF15" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG15" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="DI15" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="DJ15" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK15" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL15" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM15" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN15" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="DP15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX15" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ15" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK15" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL15" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO15" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP15" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER15" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="ES15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV15" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW15" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX15" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" t="s">
+        <v>333</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J16" t="s">
+        <v>161</v>
+      </c>
+      <c r="K16" t="s">
+        <v>158</v>
+      </c>
+      <c r="L16" t="s">
+        <v>158</v>
+      </c>
+      <c r="M16" t="s">
+        <v>158</v>
+      </c>
+      <c r="N16" t="s">
+        <v>158</v>
+      </c>
+      <c r="O16" t="s">
+        <v>158</v>
+      </c>
+      <c r="P16" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>158</v>
+      </c>
+      <c r="R16" t="s">
+        <v>158</v>
+      </c>
+      <c r="S16" t="s">
+        <v>158</v>
+      </c>
+      <c r="T16" t="s">
+        <v>158</v>
+      </c>
+      <c r="U16" t="s">
+        <v>162</v>
+      </c>
+      <c r="V16" t="s">
+        <v>162</v>
+      </c>
+      <c r="W16" t="s">
+        <v>162</v>
+      </c>
+      <c r="X16" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>60</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR16">
+        <v>6</v>
+      </c>
+      <c r="AS16">
+        <v>30</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU16">
+        <v>3</v>
+      </c>
+      <c r="AV16">
+        <v>60</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX16">
+        <v>2</v>
+      </c>
+      <c r="AY16">
+        <v>120</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA16">
+        <v>1</v>
+      </c>
+      <c r="BB16">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD16">
+        <v>1</v>
+      </c>
+      <c r="BE16">
+        <v>20</v>
+      </c>
+      <c r="BF16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="BG16" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="BH16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BI16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="BL16" s="2"/>
+      <c r="BM16" s="2"/>
+      <c r="BN16" s="2"/>
+      <c r="BO16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP16" s="2"/>
+      <c r="BQ16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="BR16" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="BS16" s="2"/>
+      <c r="BT16" s="2"/>
+      <c r="BU16" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ16" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB16" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC16" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE16" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI16" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK16" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL16" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN16" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO16" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP16" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ16" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR16" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU16" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ16" s="2"/>
+      <c r="DA16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE16" s="2"/>
+      <c r="DF16" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="DG16" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH16" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="DI16" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="DJ16" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK16" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL16" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN16" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="DP16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS16" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU16" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH16" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK16" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN16" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO16" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ16" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="ES16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV16" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX16" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" t="s">
+        <v>340</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" t="s">
+        <v>158</v>
+      </c>
+      <c r="J17" t="s">
+        <v>161</v>
+      </c>
+      <c r="K17" t="s">
+        <v>158</v>
+      </c>
+      <c r="L17" t="s">
+        <v>158</v>
+      </c>
+      <c r="M17" t="s">
+        <v>158</v>
+      </c>
+      <c r="N17" t="s">
+        <v>158</v>
+      </c>
+      <c r="O17" t="s">
+        <v>158</v>
+      </c>
+      <c r="P17" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>158</v>
+      </c>
+      <c r="R17" t="s">
+        <v>158</v>
+      </c>
+      <c r="S17" t="s">
+        <v>158</v>
+      </c>
+      <c r="T17" t="s">
+        <v>158</v>
+      </c>
+      <c r="U17" t="s">
+        <v>162</v>
+      </c>
+      <c r="V17" t="s">
+        <v>162</v>
+      </c>
+      <c r="W17" t="s">
+        <v>162</v>
+      </c>
+      <c r="X17" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO17">
+        <v>5</v>
+      </c>
+      <c r="AP17">
+        <v>60</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR17">
+        <v>6</v>
+      </c>
+      <c r="AS17">
+        <v>30</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU17">
+        <v>3</v>
+      </c>
+      <c r="AV17">
+        <v>120</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX17">
+        <v>2</v>
+      </c>
+      <c r="AY17">
+        <v>100</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA17">
+        <v>1</v>
+      </c>
+      <c r="BB17">
+        <v>20</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD17">
+        <v>1</v>
+      </c>
+      <c r="BE17">
+        <v>20</v>
+      </c>
+      <c r="BF17" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="BG17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="BH17" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="BI17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK17" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="BL17" s="2"/>
+      <c r="BM17" s="2"/>
+      <c r="BN17" s="2"/>
+      <c r="BO17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP17" s="2"/>
+      <c r="BQ17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BR17" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BS17" s="2"/>
+      <c r="BT17" s="2"/>
+      <c r="BU17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB17" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC17" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD17" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI17" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ17" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL17" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN17" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO17" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP17" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ17" s="2"/>
+      <c r="DA17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE17" s="2"/>
+      <c r="DF17" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG17" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH17" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="DI17" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="DJ17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK17" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL17" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO17" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="DP17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ17" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS17" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT17" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU17" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED17" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG17" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI17" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM17" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP17" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER17" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="ES17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV17" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX17" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C18" t="s">
+        <v>347</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I18" t="s">
+        <v>158</v>
+      </c>
+      <c r="J18" t="s">
+        <v>161</v>
+      </c>
+      <c r="K18" t="s">
+        <v>158</v>
+      </c>
+      <c r="L18" t="s">
+        <v>158</v>
+      </c>
+      <c r="M18" t="s">
+        <v>158</v>
+      </c>
+      <c r="N18" t="s">
+        <v>158</v>
+      </c>
+      <c r="O18" t="s">
+        <v>158</v>
+      </c>
+      <c r="P18" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>158</v>
+      </c>
+      <c r="R18" t="s">
+        <v>158</v>
+      </c>
+      <c r="S18" t="s">
+        <v>158</v>
+      </c>
+      <c r="T18" t="s">
+        <v>158</v>
+      </c>
+      <c r="U18" t="s">
+        <v>162</v>
+      </c>
+      <c r="V18" t="s">
+        <v>162</v>
+      </c>
+      <c r="W18" t="s">
+        <v>162</v>
+      </c>
+      <c r="X18" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO18">
+        <v>5</v>
+      </c>
+      <c r="AP18">
+        <v>60</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR18">
+        <v>6</v>
+      </c>
+      <c r="AS18">
+        <v>30</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU18">
+        <v>3</v>
+      </c>
+      <c r="AV18">
+        <v>45</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX18">
+        <v>2</v>
+      </c>
+      <c r="AY18">
+        <v>60</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA18">
+        <v>1</v>
+      </c>
+      <c r="BB18">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD18">
+        <v>1</v>
+      </c>
+      <c r="BE18">
+        <v>20</v>
+      </c>
+      <c r="BF18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="BG18" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="BH18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ18" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK18" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="BL18" s="2"/>
+      <c r="BM18" s="2"/>
+      <c r="BN18" s="2"/>
+      <c r="BO18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP18" s="2"/>
+      <c r="BQ18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BR18" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="BS18" s="2"/>
+      <c r="BT18" s="2"/>
+      <c r="BU18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB18" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC18" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD18" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG18" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI18" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM18" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN18" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO18" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP18" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ18" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR18" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU18" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ18" s="2"/>
+      <c r="DA18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE18" s="2"/>
+      <c r="DF18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="DG18" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="DI18" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="DJ18" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK18" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL18" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM18" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN18" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO18" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="DP18" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ18" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR18" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS18" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT18" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU18" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX18" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED18" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG18" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH18" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI18" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ18" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK18" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM18" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN18" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP18" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER18" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="ES18" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET18" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU18" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV18" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW18" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX18" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:154" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" t="s">
+        <v>351</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19" t="s">
+        <v>158</v>
+      </c>
+      <c r="J19" t="s">
+        <v>161</v>
+      </c>
+      <c r="K19" t="s">
+        <v>158</v>
+      </c>
+      <c r="L19" t="s">
+        <v>158</v>
+      </c>
+      <c r="M19" t="s">
+        <v>158</v>
+      </c>
+      <c r="N19" t="s">
+        <v>158</v>
+      </c>
+      <c r="O19" t="s">
+        <v>158</v>
+      </c>
+      <c r="P19" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>158</v>
+      </c>
+      <c r="R19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S19" t="s">
+        <v>158</v>
+      </c>
+      <c r="T19" t="s">
+        <v>158</v>
+      </c>
+      <c r="U19" t="s">
+        <v>162</v>
+      </c>
+      <c r="V19" t="s">
+        <v>162</v>
+      </c>
+      <c r="W19" t="s">
+        <v>162</v>
+      </c>
+      <c r="X19" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>158</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO19">
+        <v>3</v>
+      </c>
+      <c r="AP19">
+        <v>22</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR19">
+        <v>6</v>
+      </c>
+      <c r="AS19">
+        <v>30</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AU19">
+        <v>3</v>
+      </c>
+      <c r="AV19">
+        <v>120</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>160</v>
+      </c>
+      <c r="AX19">
+        <v>2</v>
+      </c>
+      <c r="AY19">
+        <v>100</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA19">
+        <v>1</v>
+      </c>
+      <c r="BB19">
+        <v>20</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>160</v>
+      </c>
+      <c r="BD19">
+        <v>1</v>
+      </c>
+      <c r="BE19">
+        <v>20</v>
+      </c>
+      <c r="BF19" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="BG19" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="BH19" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="BI19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="BK19" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="BL19" s="2"/>
+      <c r="BM19" s="2"/>
+      <c r="BN19" s="2"/>
+      <c r="BO19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP19" s="2"/>
+      <c r="BQ19" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="BR19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BS19" s="2"/>
+      <c r="BT19" s="2"/>
+      <c r="BU19" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="BV19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BW19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BY19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BZ19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CA19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CB19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="CC19" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="CD19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="CE19" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="CF19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CG19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="CH19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CI19" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CJ19" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="CK19" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="CM19" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="CN19" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="CO19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CP19" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="CQ19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="CR19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="CS19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CT19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="CU19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="CV19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CW19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CX19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CY19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CZ19" s="2"/>
+      <c r="DA19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DB19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DC19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DD19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DE19" s="2"/>
+      <c r="DF19" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="DG19" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="DH19" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="DI19" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="DJ19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="DK19" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="DL19" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="DM19" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="DN19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="DO19" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="DP19" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="DQ19" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="DR19" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="DS19" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="DT19" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="DU19" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="DV19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DW19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="DX19" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="DY19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DZ19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EA19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EB19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EC19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ED19" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EE19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EF19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="EG19" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EH19" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="EI19" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="EJ19" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="EK19" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="EL19" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="EM19" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="EN19" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="EO19" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="EP19" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="EQ19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="ER19" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="ES19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="ET19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EU19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV19" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="EW19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="EX19" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="50">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Belum Menikah,Menikah,Cerai Mati,Cerai Hidup"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F4 H2:I4 K2:T4 Y2:AE4 AI2:AI4 AL2:AL4 AN2:AN4 AQ2:AQ4 AT2:AT4 AW2:AW4 AZ2:AZ4 BC2:BC4 BI2:BI4 BO2:BO4 BV2:BZ4 CU2:CX4 DA2:DD4 DY2:EB4" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F19 H2:I19 K2:T19 Y2:AE19 AI2:AI19 AL2:AL19 AN2:AN19 AQ2:AQ19 AT2:AT19 AW2:AW19 AZ2:AZ19 BC2:BC19 BI2:BI19 BO2:BO19 BV2:BZ19 CU2:CX19 DA2:DD19 DY2:EB19" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Ya,Tidak"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G4" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G19" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Non disabilitas,Penyandang disabilitas"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J4 AF2:AF4 BU2:BU4 CE2:CE4 EM2:EM3" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:X4" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J19 AF2:AF19 BU2:BU19 CE2:CE19 EM2:EM3" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:X19" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Tidak sama sekali,Kurang dari 1 minggu,Lebih dari 1 minggu,Hampir setiap hari"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK4" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK19" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"1 s.d &lt;10 tahun lalu,10 s.d &lt;15 tahun lalu,15 tahun lalu atau lebih"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN4" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN2:BN19" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"True,False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA2:CA4" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA2:CA19" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"Normal,Abnormal TBC,Abnormal non TBC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB4" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CB2:CB19" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"Riwayat kontak serumah,Riwayat kontak erat,Tidak ada,Tidak diketahui"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2:CC4" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC2:CC19" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"Bakteriologis,Klinis"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CD2:CD4" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CD2:CD19" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"TCM,BTA,NPOC,Tidak dilakukan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CF2:CF4" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CF2:CF19" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>"Suspek frambusia,Bukan frambusia,Tidak Ada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CG2:CG4 ES2:EW4" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CG2:CG19 ES2:EW19" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"Reaktif,Non Reaktif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CH2:CH4" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CH2:CH19" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"Kusta,Bukan kusta,Meragukan,Tidak Ada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CI2:CI4" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CI2:CI19" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>"Kusta,Bukan kusta,Meragukan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ2:CJ4" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ2:CJ19" xr:uid="{00000000-0002-0000-0000-00000F000000}">
       <formula1>"Skabies,Bukan Skabies,Meragukan,Tidak Ada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CK2:CK4" xr:uid="{00000000-0002-0000-0000-000010000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CK2:CK19" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>"Tidak ada serumen impaksi,Ada serumen impaksi"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CL2:CL4" xr:uid="{00000000-0002-0000-0000-000011000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CL2:CL19" xr:uid="{00000000-0002-0000-0000-000011000000}">
       <formula1>"Tidak ada infeksi telinga,Ada infeksi telinga"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM2:CM4" xr:uid="{00000000-0002-0000-0000-000012000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM2:CM19" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>"Normal,Curiga gangguan pendengaran"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN2:CN4" xr:uid="{00000000-0002-0000-0000-000013000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN2:CN19" xr:uid="{00000000-0002-0000-0000-000013000000}">
       <formula1>"Normal,Gangguan Pendengaran"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CO2:CO4" xr:uid="{00000000-0002-0000-0000-000014000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CO2:CO19" xr:uid="{00000000-0002-0000-0000-000014000000}">
       <formula1>"Normal (visus 6/6 - 6/12),Curiga gangguan penglihatan (visus &lt;6/12)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP2:CP4" xr:uid="{00000000-0002-0000-0000-000015000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP2:CP19" xr:uid="{00000000-0002-0000-0000-000015000000}">
       <formula1>"Normal (visus 6/6 - 6/12),Gangguan penglihatan ringan (visus &lt;6/12 - 6/18),Gangguan penglihatan sedang (&lt;6/18 - 6/60),Gangguan penglihatan berat (&lt;6/60 - 3/60),Buta (&lt;3/60)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CQ2:CQ4" xr:uid="{00000000-0002-0000-0000-000016000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CQ2:CQ19" xr:uid="{00000000-0002-0000-0000-000016000000}">
       <formula1>"Visus membaik,Visus tidak membaik (visus tetap)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CR2:CR4" xr:uid="{00000000-0002-0000-0000-000017000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CR2:CR19" xr:uid="{00000000-0002-0000-0000-000017000000}">
       <formula1>"Kelainan refraksi ringan (0.50 - 3.00 Dioptri),Kelainan refraksi sedang (3.00 - 6.00 Dioptri),Kelainan refraksi berat (&gt;6.00 Dioptri)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CS2:CS4" xr:uid="{00000000-0002-0000-0000-000018000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CS2:CS19" xr:uid="{00000000-0002-0000-0000-000018000000}">
       <formula1>"Normal,Curiga kelainan mata"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CT2:CT4" xr:uid="{00000000-0002-0000-0000-000019000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CT2:CT19" xr:uid="{00000000-0002-0000-0000-000019000000}">
       <formula1>"Curiga katarak,Normal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY2:CY4" xr:uid="{00000000-0002-0000-0000-00001A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY2:CY19" xr:uid="{00000000-0002-0000-0000-00001A000000}">
       <formula1>"Iya,Tidak"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CZ2:CZ4" xr:uid="{00000000-0002-0000-0000-00001B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CZ2:CZ19" xr:uid="{00000000-0002-0000-0000-00001B000000}">
       <formula1>"&lt;20 bungkus per tahun,20-30 bungkus per tahun,&gt;30 bungkus per tahun"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DL2:DL4" xr:uid="{00000000-0002-0000-0000-00001C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DL2:DL19" xr:uid="{00000000-0002-0000-0000-00001C000000}">
       <formula1>"HBsAg Non Reaktif,HBsAg Reaktif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DM2:DM4" xr:uid="{00000000-0002-0000-0000-00001D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DM2:DM19" xr:uid="{00000000-0002-0000-0000-00001D000000}">
       <formula1>"Anti HCV Non Reaktif,Anti HCV Reaktif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DN2:DN4" xr:uid="{00000000-0002-0000-0000-00001E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DN2:DN19" xr:uid="{00000000-0002-0000-0000-00001E000000}">
       <formula1>"VL HCV RNA Negatif,VL HCV RNA Positif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EE2:EE4" xr:uid="{00000000-0002-0000-0000-00001F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EE2:EE19" xr:uid="{00000000-0002-0000-0000-00001F000000}">
       <formula1>"Normal,Abnormal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EF2:EF4" xr:uid="{00000000-0002-0000-0000-000020000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EF2:EF19" xr:uid="{00000000-0002-0000-0000-000020000000}">
       <formula1>"Normal,Abnormal ST Depresi,Abnormal T Inversi,Abnormal Hipertrofi Ventrikel Kiri,Abnormal Atrial Fibrilasi,Abnormal Q-Patologis,Abnormal ST Elevasi,Abnormal Gambaran Abnormal Lainnya"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EG2:EG4" xr:uid="{00000000-0002-0000-0000-000021000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EG2:EG19" xr:uid="{00000000-0002-0000-0000-000021000000}">
       <formula1>"Bersedia,Menolak,Tidak tahu"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EH2:EH4" xr:uid="{00000000-0002-0000-0000-000022000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EH2:EH19" xr:uid="{00000000-0002-0000-0000-000022000000}">
       <formula1>"Ditemukan benjolan,Tidak ditemukan benjolan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ED2:ED4 EI2:EI4" xr:uid="{00000000-0002-0000-0000-000023000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ED2:ED19 EI2:EI19" xr:uid="{00000000-0002-0000-0000-000023000000}">
       <formula1>"Negatif,Positif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EJ2:EJ4" xr:uid="{00000000-0002-0000-0000-000024000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EJ2:EJ19" xr:uid="{00000000-0002-0000-0000-000024000000}">
       <formula1>"Memiliki diagnosis kanker &gt;5 tahun yang lalu,Memiliki diagnosis kanker &lt;5 tahun yang lalu,Tidak pernah didiagnosis menderita kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EK2:EK4" xr:uid="{00000000-0002-0000-0000-000025000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EK2:EK19" xr:uid="{00000000-0002-0000-0000-000025000000}">
       <formula1>"Memiliki keluarga yang terdiagnosis kanker paru,Memiliki keluarga yang terdiagnosis kanker lain,Tidak ada keluarga yang terdiagnosis kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EL2:EL4" xr:uid="{00000000-0002-0000-0000-000026000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EL2:EL19" xr:uid="{00000000-0002-0000-0000-000026000000}">
       <formula1>"Perokok aktif (dalam 1 tahun ini masih merokok),Perokok/bekas perokok berhenti &lt;10 tahun lalu,Perokok pasif dari lingkungan rumah/tempat kerja,Tidak pernah merokok"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EN2:EN4" xr:uid="{00000000-0002-0000-0000-000027000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EN2:EN19" xr:uid="{00000000-0002-0000-0000-000027000000}">
       <formula1>"Memiliki tempat tinggal berpotensi tinggi,Tidak yakin memiliki tempat tinggal berpotensi tinggi,Tidak memiliki tempat tinggal berpotensi tinggi"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EO2:EO4" xr:uid="{00000000-0002-0000-0000-000028000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EO2:EO19" xr:uid="{00000000-0002-0000-0000-000028000000}">
       <formula1>"Memiliki lingkungan dalam rumah yang tidak sehat,Tidak yakin memiliki lingkungan dalam rumah yang tidak sehat,Memiliki lingkungan dalam rumah yang sehat"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EQ2:EQ4" xr:uid="{00000000-0002-0000-0000-000029000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EQ2:EQ19" xr:uid="{00000000-0002-0000-0000-000029000000}">
       <formula1>"Normal,Tidak Normal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DU2:DU4" xr:uid="{00000000-0002-0000-0000-00002A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DU2:DU19" xr:uid="{00000000-0002-0000-0000-00002A000000}">
       <formula1>"SADANIS,USG Payudara"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DV2:DV4" xr:uid="{00000000-0002-0000-0000-00002B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DV2:DV19" xr:uid="{00000000-0002-0000-0000-00002B000000}">
       <formula1>"Normal,Ditemukan benjolan,Curiga kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DW2:DW4" xr:uid="{00000000-0002-0000-0000-00002C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DW2:DW19" xr:uid="{00000000-0002-0000-0000-00002C000000}">
       <formula1>" Normal,Simple cyst,Non simple cyst"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DX2:DX4" xr:uid="{00000000-0002-0000-0000-00002D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DX2:DX19" xr:uid="{00000000-0002-0000-0000-00002D000000}">
       <formula1>"HPV Negatif,HPV Positif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EC2:EC4" xr:uid="{00000000-0002-0000-0000-00002E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EC2:EC19" xr:uid="{00000000-0002-0000-0000-00002E000000}">
       <formula1>"Normal,Curiga kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM4" xr:uid="{00000000-0002-0000-0000-00002F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM19" xr:uid="{00000000-0002-0000-0000-00002F000000}">
       <formula1>"Pernah imunisasi tetanus minimal dua kali,Pernah imunisasi tetanus satu kali,Pernah imunisasi tetanus tetapi tidak ingat berapa kali,Tidak tahu atau tidak ingat"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EM4" xr:uid="{00000000-0002-0000-0000-000030000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EM4:EM19" xr:uid="{00000000-0002-0000-0000-000030000000}">
       <formula1>"Tidak yakin tempat kerja mengandung zat karsinogenik"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP2:EP4" xr:uid="{00000000-0002-0000-0000-000031000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP2:EP19" xr:uid="{00000000-0002-0000-0000-000031000000}">
       <formula1>"Pernah didiagnosis tuberkulosis (TBC)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/dataset/dewasa.xlsx
+++ b/dataset/dewasa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbokprom12021/PycharmProjects/CKG-Helper/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC9CC0E-6DD4-7F4B-BBBF-023EAF915E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A112EB-50C8-4943-A239-3B0E147827D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="4500" yWindow="-21000" windowWidth="36000" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="3300" yWindow="-21000" windowWidth="19200" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BS1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+    <comment ref="BU1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
       <text>
         <r>
           <rPr>
@@ -358,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BT1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+    <comment ref="BV1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
       <text>
         <r>
           <rPr>
@@ -373,7 +373,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BU1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
+    <comment ref="BW1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
       <text>
         <r>
           <rPr>
@@ -388,7 +388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BY1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
+    <comment ref="CB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
       <text>
         <r>
           <rPr>
@@ -403,7 +403,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CJ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+    <comment ref="CN1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -418,7 +418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CL1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
+    <comment ref="CQ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -433,7 +433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CP1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
+    <comment ref="CV1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -448,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CR1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
+    <comment ref="CY1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -463,7 +463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CW1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
+    <comment ref="DF1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -478,7 +478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CY1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
+    <comment ref="DH1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -493,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="CZ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
+    <comment ref="DI1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
       <text>
         <r>
           <rPr>
@@ -508,7 +508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
+    <comment ref="DJ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
       <text>
         <r>
           <rPr>
@@ -523,7 +523,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
+    <comment ref="DK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
       <text>
         <r>
           <rPr>
@@ -538,7 +538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DI1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
+    <comment ref="DU1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
       <text>
         <r>
           <rPr>
@@ -553,7 +553,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="DW1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
+    <comment ref="EM1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
       <text>
         <r>
           <rPr>
@@ -568,7 +568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EE1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
+    <comment ref="EX1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
       <text>
         <r>
           <rPr>
@@ -583,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EF1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
+    <comment ref="EY1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
       <text>
         <r>
           <rPr>
@@ -598,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EH1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
+    <comment ref="FB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
       <text>
         <r>
           <rPr>
@@ -613,7 +613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EI1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
+    <comment ref="FC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
       <text>
         <r>
           <rPr>
@@ -628,7 +628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EJ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
+    <comment ref="FD1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
       <text>
         <r>
           <rPr>
@@ -643,7 +643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="EK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
+    <comment ref="FE1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -658,7 +658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
+    <comment ref="GC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -673,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FD1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C000000}">
+    <comment ref="GD1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -688,7 +688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="FE1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D000000}">
+    <comment ref="GE1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -708,7 +708,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="260">
   <si>
     <t>batas_awal</t>
   </si>
@@ -1416,6 +1416,78 @@
   </si>
   <si>
     <t>skrining_demografi</t>
+  </si>
+  <si>
+    <t>skrining_gizi</t>
+  </si>
+  <si>
+    <t>skrining_gula_darah_dewasa</t>
+  </si>
+  <si>
+    <t>skrining_tekanan_darah_dewasa</t>
+  </si>
+  <si>
+    <t>skrining_tb</t>
+  </si>
+  <si>
+    <t>skrining_frambusia</t>
+  </si>
+  <si>
+    <t>skrining_kusta</t>
+  </si>
+  <si>
+    <t>skrining_skabies</t>
+  </si>
+  <si>
+    <t>skrining_telinga_mata</t>
+  </si>
+  <si>
+    <t>skrining_karies</t>
+  </si>
+  <si>
+    <t>skrining_periodontal</t>
+  </si>
+  <si>
+    <t>skrining_ppok</t>
+  </si>
+  <si>
+    <t>skrining_kadar_co</t>
+  </si>
+  <si>
+    <t>skrining_lipid</t>
+  </si>
+  <si>
+    <t>skrining_fibrosis</t>
+  </si>
+  <si>
+    <t>skrining_hepatitis</t>
+  </si>
+  <si>
+    <t>skrining_fungsi_ginjal</t>
+  </si>
+  <si>
+    <t>skrining_kerusakan_ginjal</t>
+  </si>
+  <si>
+    <t>skrining_kanker_payudara</t>
+  </si>
+  <si>
+    <t>skrining_hpv_dna</t>
+  </si>
+  <si>
+    <t>skrining_inspekulo_iva</t>
+  </si>
+  <si>
+    <t>skrining_jantung</t>
+  </si>
+  <si>
+    <t>skrining_catin_perempuan</t>
+  </si>
+  <si>
+    <t>skrining_hiv</t>
+  </si>
+  <si>
+    <t>skrining_sifilis</t>
   </si>
 </sst>
 </file>
@@ -1469,7 +1541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1493,6 +1565,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1827,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FG19"/>
+  <dimension ref="A1:GH19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="1" bestFit="1" customWidth="1"/>
@@ -1890,93 +1965,120 @@
     <col min="63" max="63" width="16" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="14.33203125" style="4" customWidth="1"/>
-    <col min="69" max="69" width="14.33203125" style="1" customWidth="1"/>
-    <col min="70" max="70" width="14.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="18.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="17.1640625" style="1" customWidth="1"/>
-    <col min="75" max="75" width="17.1640625" style="2" customWidth="1"/>
-    <col min="76" max="76" width="16" style="4" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="6.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="25" style="4" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="23.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="14.83203125" style="4" customWidth="1"/>
-    <col min="89" max="89" width="21.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="22.83203125" style="4" customWidth="1"/>
-    <col min="93" max="93" width="16.1640625" style="4" customWidth="1"/>
-    <col min="94" max="94" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="95" max="96" width="12.33203125" style="4" customWidth="1"/>
-    <col min="97" max="97" width="14.1640625" style="1" customWidth="1"/>
-    <col min="98" max="98" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="23.6640625" style="1" customWidth="1"/>
-    <col min="100" max="100" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="26" style="1" customWidth="1"/>
-    <col min="102" max="102" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="41.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="12.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="108" max="109" width="12.83203125" style="1" customWidth="1"/>
-    <col min="110" max="110" width="18.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="17.5" style="1" customWidth="1"/>
-    <col min="112" max="112" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="19.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="115" max="117" width="19.5" style="1" customWidth="1"/>
-    <col min="118" max="118" width="9.83203125" style="1" customWidth="1"/>
-    <col min="119" max="122" width="11.5" style="1" customWidth="1"/>
-    <col min="123" max="123" width="4.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="18.1640625" style="1" customWidth="1"/>
-    <col min="128" max="128" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="129" max="131" width="8.33203125" style="4" customWidth="1"/>
-    <col min="132" max="132" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="20.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="20.5" style="4" customWidth="1"/>
-    <col min="138" max="140" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="17.1640625" style="4" customWidth="1"/>
-    <col min="143" max="143" width="17.1640625" style="1" customWidth="1"/>
-    <col min="144" max="144" width="14" style="1" customWidth="1"/>
-    <col min="145" max="145" width="15.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="18.1640625" style="1" customWidth="1"/>
-    <col min="147" max="147" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="11.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="18.1640625" style="4" customWidth="1"/>
-    <col min="150" max="151" width="18.1640625" style="1" customWidth="1"/>
-    <col min="152" max="152" width="46.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="43.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="37.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="156" max="156" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="10.33203125" style="4" customWidth="1"/>
-    <col min="159" max="159" width="10.33203125" style="1" customWidth="1"/>
-    <col min="160" max="160" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="10.33203125" style="1" customWidth="1"/>
-    <col min="162" max="162" width="14.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="19" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="68" max="69" width="14.33203125" style="4" customWidth="1"/>
+    <col min="70" max="70" width="14.33203125" style="1" customWidth="1"/>
+    <col min="71" max="71" width="24.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="14.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.1640625" style="1" customWidth="1"/>
+    <col min="77" max="77" width="17.1640625" style="2" customWidth="1"/>
+    <col min="78" max="78" width="28.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="6.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="8" style="4" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="15" style="12" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="25" style="4" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="14.83203125" style="4" customWidth="1"/>
+    <col min="93" max="93" width="14.83203125" style="12" customWidth="1"/>
+    <col min="94" max="94" width="21.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="22.83203125" style="4" customWidth="1"/>
+    <col min="98" max="98" width="22.83203125" style="12" customWidth="1"/>
+    <col min="99" max="99" width="16.1640625" style="4" customWidth="1"/>
+    <col min="100" max="100" width="19.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="19.83203125" style="12" customWidth="1"/>
+    <col min="102" max="103" width="12.33203125" style="4" customWidth="1"/>
+    <col min="104" max="104" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="14.1640625" style="1" customWidth="1"/>
+    <col min="106" max="106" width="18.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="23.6640625" style="1" customWidth="1"/>
+    <col min="109" max="109" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="26" style="1" customWidth="1"/>
+    <col min="111" max="111" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="41.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="12.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="12.83203125" style="12" customWidth="1"/>
+    <col min="118" max="119" width="12.83203125" style="1" customWidth="1"/>
+    <col min="120" max="120" width="17.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="18.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="17.5" style="1" customWidth="1"/>
+    <col min="123" max="123" width="17.5" style="12" customWidth="1"/>
+    <col min="124" max="124" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="127" max="129" width="19.5" style="1" customWidth="1"/>
+    <col min="130" max="130" width="19.5" style="12" customWidth="1"/>
+    <col min="131" max="131" width="9.83203125" style="1" customWidth="1"/>
+    <col min="132" max="132" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="133" max="136" width="11.5" style="1" customWidth="1"/>
+    <col min="137" max="137" width="14" style="12" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="4.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="15.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="16.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="18.1640625" style="1" customWidth="1"/>
+    <col min="144" max="144" width="18.1640625" style="12" customWidth="1"/>
+    <col min="145" max="145" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="146" max="148" width="8.33203125" style="4" customWidth="1"/>
+    <col min="149" max="149" width="21.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="22.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="20.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="17.33203125" style="11" customWidth="1"/>
+    <col min="157" max="157" width="20.5" style="4" customWidth="1"/>
+    <col min="158" max="160" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="17.1640625" style="11" customWidth="1"/>
+    <col min="163" max="163" width="17.1640625" style="4" customWidth="1"/>
+    <col min="164" max="164" width="17.1640625" style="1" customWidth="1"/>
+    <col min="165" max="165" width="12.33203125" style="12" customWidth="1"/>
+    <col min="166" max="166" width="14" style="1" customWidth="1"/>
+    <col min="167" max="167" width="15.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="18.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="169" max="169" width="18.1640625" style="1" customWidth="1"/>
+    <col min="170" max="170" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="11.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="18.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="18.1640625" style="4" customWidth="1"/>
+    <col min="174" max="175" width="18.1640625" style="1" customWidth="1"/>
+    <col min="176" max="176" width="46.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="43.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="37.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="22.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="10.6640625" style="11" customWidth="1"/>
+    <col min="184" max="184" width="10.33203125" style="4" customWidth="1"/>
+    <col min="185" max="185" width="10.33203125" style="1" customWidth="1"/>
+    <col min="186" max="186" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="10.33203125" style="1" customWidth="1"/>
+    <col min="188" max="188" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="14.5" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:163" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:190" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2175,299 +2277,380 @@
       <c r="BN1" t="s">
         <v>56</v>
       </c>
-      <c r="BO1" s="4" t="s">
+      <c r="BO1" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="BP1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BP1" s="4" t="s">
+      <c r="BQ1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BR1" s="4" t="s">
+      <c r="BS1" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="BT1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="BZ1" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="CA1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="CC1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CD1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CD1" s="4" t="s">
+      <c r="CG1" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="CH1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CJ1" s="4" t="s">
+      <c r="CN1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="CK1" s="4" t="s">
+      <c r="CO1" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="CP1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CN1" s="4" t="s">
+      <c r="CS1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="CO1" s="4" t="s">
+      <c r="CT1" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="CU1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="CQ1" s="4" t="s">
+      <c r="CW1" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="CX1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="CR1" s="4" t="s">
+      <c r="CY1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CZ1" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="DA1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="DB1" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="DC1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="DC1" s="4" t="s">
+      <c r="DL1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DM1" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="DN1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DP1" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="DQ1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DS1" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="DT1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DX1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DY1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DZ1" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="EA1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="EB1" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="EC1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="ED1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="EE1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="EF1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="EG1" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="EH1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="EI1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="EJ1" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="EK1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="EL1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="DW1" s="1" t="s">
+      <c r="EM1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="DX1" s="3" t="s">
+      <c r="EN1" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="EO1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="DY1" s="4" t="s">
+      <c r="EP1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="DZ1" s="4" t="s">
+      <c r="EQ1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="EA1" s="4" t="s">
+      <c r="ER1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="EB1" s="4" t="s">
+      <c r="ES1" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="ET1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="EC1" s="4" t="s">
+      <c r="EU1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="ED1" s="1" t="s">
+      <c r="EV1" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="EW1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="EE1" s="1" t="s">
+      <c r="EX1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="EF1" s="4" t="s">
+      <c r="EY1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="EG1" s="4" t="s">
+      <c r="EZ1" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="FA1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="EH1" s="1" t="s">
+      <c r="FB1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="EI1" s="1" t="s">
+      <c r="FC1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="EJ1" s="1" t="s">
+      <c r="FD1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="EK1" s="1" t="s">
+      <c r="FE1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="EL1" s="4" t="s">
+      <c r="FF1" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="FG1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="EM1" s="1" t="s">
+      <c r="FH1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="EN1" s="1" t="s">
+      <c r="FI1" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="FJ1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="EO1" s="4" t="s">
+      <c r="FK1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="EP1" s="1" t="s">
+      <c r="FL1" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="FM1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="EQ1" s="1" t="s">
+      <c r="FN1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="ER1" s="4" t="s">
+      <c r="FO1" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="ES1" s="4" t="s">
+      <c r="FP1" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="FQ1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="ET1" s="1" t="s">
+      <c r="FR1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="EU1" s="1" t="s">
+      <c r="FS1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="EV1" s="1" t="s">
+      <c r="FT1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="EW1" s="1" t="s">
+      <c r="FU1" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="EX1" s="1" t="s">
+      <c r="FV1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="EY1" s="4" t="s">
+      <c r="FW1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="EZ1" s="1" t="s">
+      <c r="FX1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="FA1" s="1" t="s">
+      <c r="FY1" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="FZ1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="FB1" s="4" t="s">
+      <c r="GA1" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="GB1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="FC1" s="1" t="s">
+      <c r="GC1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="FD1" s="1" t="s">
+      <c r="GD1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="FE1" s="1" t="s">
+      <c r="GE1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="FF1" s="1" t="s">
+      <c r="GF1" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="GG1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="FG1" t="s">
+      <c r="GH1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:163" s="7" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:190" s="7" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>154</v>
       </c>
@@ -2666,299 +2849,380 @@
       <c r="BN2" s="7">
         <v>20</v>
       </c>
-      <c r="BO2" s="8" t="s">
+      <c r="BO2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="BP2" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="BP2" s="8" t="s">
+      <c r="BQ2" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="BQ2" s="8" t="s">
+      <c r="BR2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BR2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="BS2" s="8" t="s">
+      <c r="BS2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="BT2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="BU2" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="BT2" s="8" t="s">
+      <c r="BV2" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="BU2" s="8" t="s">
+      <c r="BW2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BV2" s="8" t="s">
+      <c r="BX2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BW2" s="8" t="s">
+      <c r="BY2" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="BX2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="BY2" s="8" t="s">
+      <c r="BZ2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CA2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CB2" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="BZ2" s="8" t="s">
+      <c r="CC2" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="CA2" s="8" t="s">
+      <c r="CD2" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="CB2" s="8" t="s">
+      <c r="CE2" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="CC2" s="8" t="s">
+      <c r="CF2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="CD2" s="8" t="s">
+      <c r="CG2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CH2" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="CE2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CF2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CG2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CH2" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="CI2" s="8" t="s">
         <v>164</v>
       </c>
       <c r="CJ2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CK2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CL2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CM2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CN2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="CK2" s="8" t="s">
+      <c r="CO2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CP2" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="CL2" s="8" t="s">
+      <c r="CQ2" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="CM2" s="8" t="s">
+      <c r="CR2" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="CN2" s="8" t="s">
+      <c r="CS2" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="CO2" s="8" t="s">
+      <c r="CT2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CU2" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CP2" s="8" t="s">
+      <c r="CV2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="CQ2" s="8" t="s">
+      <c r="CW2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CX2" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="CR2" s="8" t="s">
+      <c r="CY2" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="CS2" s="8" t="s">
+      <c r="CZ2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DA2" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CT2" s="8" t="s">
+      <c r="DB2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DC2" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="CU2" s="8" t="s">
+      <c r="DD2" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="CV2" s="8" t="s">
+      <c r="DE2" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="CW2" s="8" t="s">
+      <c r="DF2" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="CX2" s="8" t="s">
+      <c r="DG2" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="CY2" s="8" t="s">
+      <c r="DH2" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="CZ2" s="8" t="s">
+      <c r="DI2" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="DA2" s="8" t="s">
+      <c r="DJ2" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="DB2" s="8" t="s">
+      <c r="DK2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="DC2" s="8" t="s">
+      <c r="DL2" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="DD2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DE2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="DF2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DG2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DH2" s="8" t="s">
+      <c r="DM2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DN2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DO2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="DP2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DQ2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DR2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DS2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DT2" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="DI2" s="8" t="s">
+      <c r="DU2" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="DJ2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DK2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DL2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DM2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DN2" s="8" t="s">
+      <c r="DV2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DW2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DX2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DY2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DZ2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EA2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="DO2" s="8" t="s">
+      <c r="EB2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EC2" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="DP2" s="8" t="s">
+      <c r="ED2" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="DQ2" s="8" t="s">
+      <c r="EE2" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="DR2" s="8" t="s">
+      <c r="EF2" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="DS2" s="8" t="s">
+      <c r="EG2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EH2" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="DT2" s="8" t="s">
+      <c r="EI2" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="DU2" s="8" t="s">
+      <c r="EJ2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EK2" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="DV2" s="8" t="s">
+      <c r="EL2" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="DW2" s="8" t="s">
+      <c r="EM2" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="DX2" s="9">
+      <c r="EN2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EO2" s="9">
         <v>0.5</v>
       </c>
-      <c r="DY2" s="8" t="s">
+      <c r="EP2" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="DZ2" s="8" t="s">
+      <c r="EQ2" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="EA2" s="8" t="s">
+      <c r="ER2" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="EB2" s="8" t="s">
+      <c r="ES2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="ET2" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="EC2" s="8" t="s">
+      <c r="EU2" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="ED2" s="8" t="s">
+      <c r="EV2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EW2" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="EE2" s="8" t="s">
+      <c r="EX2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EF2" s="8" t="s">
+      <c r="EY2" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="EG2" s="8" t="s">
+      <c r="EZ2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FA2" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="EH2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EI2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EJ2" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EK2" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="EL2" s="8" t="s">
+      <c r="FB2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FC2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FD2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FE2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="FF2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FG2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EM2" s="8" t="s">
+      <c r="FH2" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="EN2" s="8" t="s">
+      <c r="FI2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FJ2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EO2" s="8" t="s">
+      <c r="FK2" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="EP2" s="8" t="s">
+      <c r="FL2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FM2" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="EQ2" s="8" t="s">
+      <c r="FN2" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="ER2" s="8" t="s">
+      <c r="FO2" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="ES2" s="8" t="s">
+      <c r="FP2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FQ2" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="ET2" s="8" t="s">
+      <c r="FR2" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="EU2" s="8" t="s">
+      <c r="FS2" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="EV2" s="8" t="s">
+      <c r="FT2" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="EW2" s="8" t="s">
+      <c r="FU2" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="EX2" s="8" t="s">
+      <c r="FV2" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="EY2" s="8" t="s">
+      <c r="FW2" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="EZ2" s="8" t="s">
+      <c r="FX2" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="FA2" s="8" t="s">
+      <c r="FY2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FZ2" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="FB2" s="8" t="s">
+      <c r="GA2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="GB2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FC2" s="8" t="s">
+      <c r="GC2" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="FD2" s="8" t="s">
+      <c r="GD2" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="FE2" s="8" t="s">
+      <c r="GE2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FF2" s="8" t="s">
+      <c r="GF2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="GG2" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FG2" s="8" t="s">
+      <c r="GH2" s="8" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:163" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:190" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>154</v>
       </c>
@@ -3157,295 +3421,376 @@
       <c r="BN3" s="7">
         <v>20</v>
       </c>
-      <c r="BO3" s="8" t="s">
+      <c r="BO3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="BP3" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="BP3" s="8" t="s">
+      <c r="BQ3" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="BQ3" s="8" t="s">
+      <c r="BR3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BR3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="BS3" s="8" t="s">
+      <c r="BS3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="BT3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="BU3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="BT3" s="8" t="s">
+      <c r="BV3" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="BU3" s="8" t="s">
+      <c r="BW3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BV3" s="8" t="s">
+      <c r="BX3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BW3" s="8" t="s">
+      <c r="BY3" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="BX3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="BY3" s="8" t="s">
+      <c r="BZ3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CA3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CB3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="BZ3" s="8" t="s">
+      <c r="CC3" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="CA3" s="8" t="s">
+      <c r="CD3" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="CB3" s="8"/>
-      <c r="CC3" s="8"/>
-      <c r="CD3" s="8" t="s">
+      <c r="CE3" s="8"/>
+      <c r="CF3" s="8"/>
+      <c r="CG3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CH3" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="CE3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CF3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CG3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CH3" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="CI3" s="8" t="s">
         <v>164</v>
       </c>
       <c r="CJ3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CK3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CL3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CM3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CN3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="CK3" s="8" t="s">
+      <c r="CO3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CP3" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="CL3" s="8" t="s">
+      <c r="CQ3" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="CM3" s="8" t="s">
+      <c r="CR3" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="CN3" s="8" t="s">
+      <c r="CS3" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="CO3" s="8" t="s">
+      <c r="CT3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CU3" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CP3" s="8" t="s">
+      <c r="CV3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="CQ3" s="8" t="s">
+      <c r="CW3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CX3" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="CR3" s="8" t="s">
+      <c r="CY3" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="CS3" s="8" t="s">
+      <c r="CZ3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DA3" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CT3" s="8" t="s">
+      <c r="DB3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DC3" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="CU3" s="8" t="s">
+      <c r="DD3" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="CV3" s="8" t="s">
+      <c r="DE3" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="CW3" s="8" t="s">
+      <c r="DF3" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="CX3" s="8" t="s">
+      <c r="DG3" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="CY3" s="8" t="s">
+      <c r="DH3" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="CZ3" s="8" t="s">
+      <c r="DI3" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="DA3" s="8" t="s">
+      <c r="DJ3" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="DB3" s="8" t="s">
+      <c r="DK3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="DC3" s="8" t="s">
+      <c r="DL3" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="DD3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DE3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="DF3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DG3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DH3" s="8" t="s">
+      <c r="DM3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DN3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DO3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="DP3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DQ3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DR3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DS3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DT3" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="DI3" s="8" t="s">
+      <c r="DU3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="DJ3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DK3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DL3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DM3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DN3" s="8" t="s">
+      <c r="DV3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DW3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DX3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DY3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DZ3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EA3" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="DO3" s="8" t="s">
+      <c r="EB3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EC3" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="DP3" s="8" t="s">
+      <c r="ED3" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="DQ3" s="8" t="s">
+      <c r="EE3" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="DR3" s="8" t="s">
+      <c r="EF3" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="DS3" s="8" t="s">
+      <c r="EG3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EH3" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="DT3" s="8" t="s">
+      <c r="EI3" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="DU3" s="8" t="s">
+      <c r="EJ3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EK3" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="DV3" s="8" t="s">
+      <c r="EL3" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="DW3" s="8" t="s">
+      <c r="EM3" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="DX3" s="9">
+      <c r="EN3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EO3" s="9">
         <v>0.5</v>
       </c>
-      <c r="DY3" s="8" t="s">
+      <c r="EP3" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="DZ3" s="8" t="s">
+      <c r="EQ3" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="EA3" s="8" t="s">
+      <c r="ER3" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="EB3" s="8" t="s">
+      <c r="ES3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="ET3" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="EC3" s="8" t="s">
+      <c r="EU3" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="ED3" s="8" t="s">
+      <c r="EV3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EW3" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="EE3" s="8" t="s">
+      <c r="EX3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EF3" s="8" t="s">
+      <c r="EY3" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="EG3" s="8" t="s">
+      <c r="EZ3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FA3" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="EH3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EI3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EJ3" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EK3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="EL3" s="8" t="s">
+      <c r="FB3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FC3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FD3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FE3" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="FF3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FG3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EM3" s="8" t="s">
+      <c r="FH3" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="EN3" s="8" t="s">
+      <c r="FI3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FJ3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EO3" s="8" t="s">
+      <c r="FK3" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="EP3" s="8" t="s">
+      <c r="FL3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FM3" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="EQ3" s="8" t="s">
+      <c r="FN3" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="ER3" s="8" t="s">
+      <c r="FO3" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="ES3" s="8" t="s">
+      <c r="FP3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FQ3" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="ET3" s="8" t="s">
+      <c r="FR3" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="EU3" s="8" t="s">
+      <c r="FS3" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="EV3" s="8" t="s">
+      <c r="FT3" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="EW3" s="8" t="s">
+      <c r="FU3" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="EX3" s="8" t="s">
+      <c r="FV3" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="EY3" s="8" t="s">
+      <c r="FW3" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="EZ3" s="8" t="s">
+      <c r="FX3" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="FA3" s="8" t="s">
+      <c r="FY3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FZ3" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="FB3" s="8" t="s">
+      <c r="GA3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="GB3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FC3" s="8" t="s">
+      <c r="GC3" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="FD3" s="8" t="s">
+      <c r="GD3" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="FE3" s="8" t="s">
+      <c r="GE3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FF3" s="8" t="s">
+      <c r="GF3" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="GG3" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FG3" s="8" t="s">
+      <c r="GH3" s="8" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>234</v>
       </c>
@@ -3644,293 +3989,374 @@
       <c r="BN4" s="7">
         <v>20</v>
       </c>
-      <c r="BO4" s="8" t="s">
+      <c r="BO4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="BP4" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="BP4" s="8" t="s">
+      <c r="BQ4" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="BQ4" s="8" t="s">
+      <c r="BR4" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BR4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="BS4" s="8" t="s">
+      <c r="BS4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="BT4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="BU4" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="BT4" s="8" t="s">
+      <c r="BV4" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="BU4" s="8" t="s">
+      <c r="BW4" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BV4" s="8" t="s">
+      <c r="BX4" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="BW4" s="8" t="s">
+      <c r="BY4" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="BX4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="BY4" s="8" t="s">
+      <c r="BZ4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CA4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CB4" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="BZ4" s="8" t="s">
+      <c r="CC4" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="CA4" s="8" t="s">
+      <c r="CD4" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="CB4" s="8"/>
-      <c r="CC4" s="8"/>
-      <c r="CD4" s="8" t="s">
+      <c r="CE4" s="8"/>
+      <c r="CF4" s="8"/>
+      <c r="CG4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CH4" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="CE4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CF4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CG4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="CH4" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="CI4" s="8" t="s">
         <v>164</v>
       </c>
       <c r="CJ4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CK4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CL4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CM4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="CN4" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="CK4" s="8" t="s">
+      <c r="CO4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CP4" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="CL4" s="8" t="s">
+      <c r="CQ4" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="CM4" s="8" t="s">
+      <c r="CR4" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="CN4" s="8" t="s">
+      <c r="CS4" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="CO4" s="8" t="s">
+      <c r="CT4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CU4" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CP4" s="8" t="s">
+      <c r="CV4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="CQ4" s="8" t="s">
+      <c r="CW4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="CX4" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="CR4" s="8" t="s">
+      <c r="CY4" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="CS4" s="8" t="s">
+      <c r="CZ4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DA4" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="CT4" s="8" t="s">
+      <c r="DB4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DC4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="CU4" s="8" t="s">
+      <c r="DD4" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="CV4" s="8" t="s">
+      <c r="DE4" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="CW4" s="8" t="s">
+      <c r="DF4" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="CX4" s="8" t="s">
+      <c r="DG4" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="CY4" s="8" t="s">
+      <c r="DH4" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="CZ4" s="8" t="s">
+      <c r="DI4" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="DA4" s="8" t="s">
+      <c r="DJ4" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="DB4" s="8" t="s">
+      <c r="DK4" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="DC4" s="8" t="s">
+      <c r="DL4" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="DD4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DE4" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="DF4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DG4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DH4" s="8" t="s">
+      <c r="DM4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DN4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DO4" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="DP4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DQ4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DR4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DS4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="DT4" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="DI4" s="8" t="s">
+      <c r="DU4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="DJ4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DK4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DL4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DM4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="DN4" s="8" t="s">
+      <c r="DV4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DW4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DX4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DY4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="DZ4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EA4" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="DO4" s="8" t="s">
+      <c r="EB4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EC4" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="DP4" s="8" t="s">
+      <c r="ED4" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="DQ4" s="8" t="s">
+      <c r="EE4" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="DR4" s="8" t="s">
+      <c r="EF4" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="DS4" s="8" t="s">
+      <c r="EG4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EH4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="DT4" s="8" t="s">
+      <c r="EI4" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="DU4" s="8" t="s">
+      <c r="EJ4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EK4" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="DV4" s="8" t="s">
+      <c r="EL4" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="DW4" s="8" t="s">
+      <c r="EM4" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="DX4" s="9">
+      <c r="EN4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EO4" s="9">
         <v>0.5</v>
       </c>
-      <c r="DY4" s="8" t="s">
+      <c r="EP4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="DZ4" s="8" t="s">
+      <c r="EQ4" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="EA4" s="8" t="s">
+      <c r="ER4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="EB4" s="8" t="s">
+      <c r="ES4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="ET4" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="EC4" s="8" t="s">
+      <c r="EU4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="ED4" s="8" t="s">
+      <c r="EV4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="EW4" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="EE4" s="8" t="s">
+      <c r="EX4" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EF4" s="8" t="s">
+      <c r="EY4" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="EG4" s="8" t="s">
+      <c r="EZ4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FA4" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="EH4" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EI4" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EJ4" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="EK4" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="EL4" s="8" t="s">
+      <c r="FB4" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FC4" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FD4" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="FE4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="FF4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FG4" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EM4" s="8" t="s">
+      <c r="FH4" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="EN4" s="8" t="s">
+      <c r="FI4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FJ4" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="EO4" s="8" t="s">
+      <c r="FK4" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="EP4" s="8" t="s">
+      <c r="FL4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FM4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="EQ4" s="8" t="s">
+      <c r="FN4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="ER4" s="8" t="s">
+      <c r="FO4" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="ES4" s="8" t="s">
+      <c r="FP4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FQ4" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="ET4" s="8" t="s">
+      <c r="FR4" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="EU4" s="8" t="s">
+      <c r="FS4" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="EV4" s="8" t="s">
+      <c r="FT4" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="EW4" s="8" t="s">
+      <c r="FU4" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="EX4" s="8" t="s">
+      <c r="FV4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="EY4" s="8" t="s">
+      <c r="FW4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="EZ4" s="8" t="s">
+      <c r="FX4" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="FA4" s="8" t="s">
+      <c r="FY4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="FZ4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="FB4" s="8" t="s">
+      <c r="GA4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="GB4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FC4" s="8" t="s">
+      <c r="GC4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="FD4" s="8" t="s">
+      <c r="GD4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="FE4" s="8" t="s">
+      <c r="GE4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FF4" s="8" t="s">
+      <c r="GF4" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="GG4" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="FG4" s="2"/>
+      <c r="GH4" s="2"/>
     </row>
-    <row r="5" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5"/>
       <c r="D5" s="11"/>
       <c r="E5" s="1"/>
@@ -3945,46 +4371,37 @@
       <c r="AE5" s="12"/>
       <c r="AL5" s="12"/>
       <c r="AV5" s="12"/>
-      <c r="BO5" s="5"/>
       <c r="BP5" s="5"/>
-      <c r="BQ5" s="2"/>
-      <c r="BR5" s="5"/>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2"/>
+      <c r="BQ5" s="5"/>
+      <c r="BR5" s="2"/>
+      <c r="BT5" s="5"/>
       <c r="BU5" s="2"/>
       <c r="BV5" s="2"/>
-      <c r="BX5" s="5"/>
-      <c r="BY5" s="2"/>
-      <c r="BZ5" s="5"/>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2"/>
       <c r="CA5" s="5"/>
       <c r="CB5" s="2"/>
-      <c r="CC5" s="2"/>
+      <c r="CC5" s="5"/>
       <c r="CD5" s="5"/>
       <c r="CE5" s="2"/>
       <c r="CF5" s="2"/>
-      <c r="CG5" s="2"/>
-      <c r="CH5" s="2"/>
+      <c r="CH5" s="5"/>
       <c r="CI5" s="2"/>
-      <c r="CJ5" s="5"/>
-      <c r="CK5" s="5"/>
+      <c r="CJ5" s="2"/>
+      <c r="CK5" s="2"/>
       <c r="CL5" s="2"/>
       <c r="CM5" s="2"/>
       <c r="CN5" s="5"/>
-      <c r="CO5" s="5"/>
-      <c r="CP5" s="2"/>
-      <c r="CQ5" s="5"/>
-      <c r="CR5" s="5"/>
-      <c r="CS5" s="2"/>
-      <c r="CT5" s="2"/>
-      <c r="CU5" s="2"/>
+      <c r="CP5" s="5"/>
+      <c r="CQ5" s="2"/>
+      <c r="CR5" s="2"/>
+      <c r="CS5" s="5"/>
+      <c r="CU5" s="5"/>
       <c r="CV5" s="2"/>
-      <c r="CW5" s="2"/>
-      <c r="CX5" s="2"/>
-      <c r="CY5" s="2"/>
-      <c r="CZ5" s="2"/>
+      <c r="CX5" s="5"/>
+      <c r="CY5" s="5"/>
       <c r="DA5" s="2"/>
-      <c r="DB5" s="2"/>
-      <c r="DC5" s="5"/>
+      <c r="DC5" s="2"/>
       <c r="DD5" s="2"/>
       <c r="DE5" s="2"/>
       <c r="DF5" s="2"/>
@@ -3993,56 +4410,71 @@
       <c r="DI5" s="2"/>
       <c r="DJ5" s="2"/>
       <c r="DK5" s="2"/>
-      <c r="DL5" s="2"/>
-      <c r="DM5" s="2"/>
+      <c r="DL5" s="5"/>
       <c r="DN5" s="2"/>
       <c r="DO5" s="2"/>
-      <c r="DP5" s="2"/>
       <c r="DQ5" s="2"/>
       <c r="DR5" s="2"/>
-      <c r="DS5" s="2"/>
       <c r="DT5" s="2"/>
       <c r="DU5" s="2"/>
       <c r="DV5" s="2"/>
       <c r="DW5" s="2"/>
-      <c r="DX5" s="10"/>
-      <c r="DY5" s="5"/>
-      <c r="DZ5" s="5"/>
-      <c r="EA5" s="5"/>
-      <c r="EB5" s="5"/>
-      <c r="EC5" s="5"/>
+      <c r="DX5" s="2"/>
+      <c r="DY5" s="2"/>
+      <c r="EA5" s="2"/>
+      <c r="EC5" s="2"/>
       <c r="ED5" s="2"/>
       <c r="EE5" s="2"/>
-      <c r="EF5" s="5"/>
-      <c r="EG5" s="5"/>
+      <c r="EF5" s="2"/>
       <c r="EH5" s="2"/>
       <c r="EI5" s="2"/>
-      <c r="EJ5" s="2"/>
       <c r="EK5" s="2"/>
-      <c r="EL5" s="5"/>
+      <c r="EL5" s="2"/>
       <c r="EM5" s="2"/>
-      <c r="EN5" s="2"/>
-      <c r="EO5" s="5"/>
-      <c r="EP5" s="2"/>
-      <c r="EQ5" s="2"/>
+      <c r="EO5" s="10"/>
+      <c r="EP5" s="5"/>
+      <c r="EQ5" s="5"/>
       <c r="ER5" s="5"/>
-      <c r="ES5" s="5"/>
-      <c r="ET5" s="2"/>
-      <c r="EU5" s="2"/>
-      <c r="EV5" s="2"/>
+      <c r="ET5" s="5"/>
+      <c r="EU5" s="5"/>
+      <c r="EV5" s="13"/>
       <c r="EW5" s="2"/>
       <c r="EX5" s="2"/>
       <c r="EY5" s="5"/>
-      <c r="EZ5" s="2"/>
-      <c r="FA5" s="2"/>
-      <c r="FB5" s="5"/>
+      <c r="EZ5" s="13"/>
+      <c r="FA5" s="5"/>
+      <c r="FB5" s="2"/>
       <c r="FC5" s="2"/>
       <c r="FD5" s="2"/>
       <c r="FE5" s="2"/>
-      <c r="FF5" s="2"/>
-      <c r="FG5" s="2"/>
+      <c r="FF5" s="13"/>
+      <c r="FG5" s="5"/>
+      <c r="FH5" s="2"/>
+      <c r="FJ5" s="2"/>
+      <c r="FK5" s="5"/>
+      <c r="FM5" s="2"/>
+      <c r="FN5" s="2"/>
+      <c r="FO5" s="5"/>
+      <c r="FQ5" s="5"/>
+      <c r="FR5" s="2"/>
+      <c r="FS5" s="2"/>
+      <c r="FT5" s="2"/>
+      <c r="FU5" s="2"/>
+      <c r="FV5" s="2"/>
+      <c r="FW5" s="5"/>
+      <c r="FX5" s="2"/>
+      <c r="FY5" s="13"/>
+      <c r="FZ5" s="2"/>
+      <c r="GA5" s="13"/>
+      <c r="GB5" s="5"/>
+      <c r="GC5" s="2"/>
+      <c r="GD5" s="2"/>
+      <c r="GE5" s="2"/>
+      <c r="GF5" s="13"/>
+      <c r="GG5" s="2"/>
+      <c r="GH5" s="2"/>
     </row>
-    <row r="6" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6"/>
       <c r="D6" s="11"/>
       <c r="E6" s="1"/>
@@ -4057,46 +4489,37 @@
       <c r="AE6" s="12"/>
       <c r="AL6" s="12"/>
       <c r="AV6" s="12"/>
-      <c r="BO6" s="5"/>
       <c r="BP6" s="5"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="5"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
+      <c r="BQ6" s="5"/>
+      <c r="BR6" s="2"/>
+      <c r="BT6" s="5"/>
       <c r="BU6" s="2"/>
       <c r="BV6" s="2"/>
-      <c r="BX6" s="5"/>
-      <c r="BY6" s="2"/>
-      <c r="BZ6" s="5"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2"/>
       <c r="CA6" s="5"/>
       <c r="CB6" s="2"/>
-      <c r="CC6" s="2"/>
+      <c r="CC6" s="5"/>
       <c r="CD6" s="5"/>
       <c r="CE6" s="2"/>
       <c r="CF6" s="2"/>
-      <c r="CG6" s="2"/>
-      <c r="CH6" s="2"/>
+      <c r="CH6" s="5"/>
       <c r="CI6" s="2"/>
-      <c r="CJ6" s="5"/>
-      <c r="CK6" s="5"/>
+      <c r="CJ6" s="2"/>
+      <c r="CK6" s="2"/>
       <c r="CL6" s="2"/>
       <c r="CM6" s="2"/>
       <c r="CN6" s="5"/>
-      <c r="CO6" s="5"/>
-      <c r="CP6" s="2"/>
-      <c r="CQ6" s="5"/>
-      <c r="CR6" s="5"/>
-      <c r="CS6" s="2"/>
-      <c r="CT6" s="2"/>
-      <c r="CU6" s="2"/>
+      <c r="CP6" s="5"/>
+      <c r="CQ6" s="2"/>
+      <c r="CR6" s="2"/>
+      <c r="CS6" s="5"/>
+      <c r="CU6" s="5"/>
       <c r="CV6" s="2"/>
-      <c r="CW6" s="2"/>
-      <c r="CX6" s="2"/>
-      <c r="CY6" s="2"/>
-      <c r="CZ6" s="2"/>
+      <c r="CX6" s="5"/>
+      <c r="CY6" s="5"/>
       <c r="DA6" s="2"/>
-      <c r="DB6" s="2"/>
-      <c r="DC6" s="5"/>
+      <c r="DC6" s="2"/>
       <c r="DD6" s="2"/>
       <c r="DE6" s="2"/>
       <c r="DF6" s="2"/>
@@ -4105,56 +4528,71 @@
       <c r="DI6" s="2"/>
       <c r="DJ6" s="2"/>
       <c r="DK6" s="2"/>
-      <c r="DL6" s="2"/>
-      <c r="DM6" s="2"/>
+      <c r="DL6" s="5"/>
       <c r="DN6" s="2"/>
       <c r="DO6" s="2"/>
-      <c r="DP6" s="2"/>
       <c r="DQ6" s="2"/>
       <c r="DR6" s="2"/>
-      <c r="DS6" s="2"/>
       <c r="DT6" s="2"/>
       <c r="DU6" s="2"/>
       <c r="DV6" s="2"/>
       <c r="DW6" s="2"/>
-      <c r="DX6" s="10"/>
-      <c r="DY6" s="5"/>
-      <c r="DZ6" s="5"/>
-      <c r="EA6" s="5"/>
-      <c r="EB6" s="5"/>
-      <c r="EC6" s="5"/>
+      <c r="DX6" s="2"/>
+      <c r="DY6" s="2"/>
+      <c r="EA6" s="2"/>
+      <c r="EC6" s="2"/>
       <c r="ED6" s="2"/>
       <c r="EE6" s="2"/>
-      <c r="EF6" s="5"/>
-      <c r="EG6" s="5"/>
+      <c r="EF6" s="2"/>
       <c r="EH6" s="2"/>
       <c r="EI6" s="2"/>
-      <c r="EJ6" s="2"/>
       <c r="EK6" s="2"/>
-      <c r="EL6" s="5"/>
+      <c r="EL6" s="2"/>
       <c r="EM6" s="2"/>
-      <c r="EN6" s="2"/>
-      <c r="EO6" s="5"/>
-      <c r="EP6" s="2"/>
-      <c r="EQ6" s="2"/>
+      <c r="EO6" s="10"/>
+      <c r="EP6" s="5"/>
+      <c r="EQ6" s="5"/>
       <c r="ER6" s="5"/>
-      <c r="ES6" s="5"/>
-      <c r="ET6" s="2"/>
-      <c r="EU6" s="2"/>
-      <c r="EV6" s="2"/>
+      <c r="ET6" s="5"/>
+      <c r="EU6" s="5"/>
+      <c r="EV6" s="13"/>
       <c r="EW6" s="2"/>
       <c r="EX6" s="2"/>
       <c r="EY6" s="5"/>
-      <c r="EZ6" s="2"/>
-      <c r="FA6" s="2"/>
-      <c r="FB6" s="5"/>
+      <c r="EZ6" s="13"/>
+      <c r="FA6" s="5"/>
+      <c r="FB6" s="2"/>
       <c r="FC6" s="2"/>
       <c r="FD6" s="2"/>
       <c r="FE6" s="2"/>
-      <c r="FF6" s="2"/>
-      <c r="FG6" s="2"/>
+      <c r="FF6" s="13"/>
+      <c r="FG6" s="5"/>
+      <c r="FH6" s="2"/>
+      <c r="FJ6" s="2"/>
+      <c r="FK6" s="5"/>
+      <c r="FM6" s="2"/>
+      <c r="FN6" s="2"/>
+      <c r="FO6" s="5"/>
+      <c r="FQ6" s="5"/>
+      <c r="FR6" s="2"/>
+      <c r="FS6" s="2"/>
+      <c r="FT6" s="2"/>
+      <c r="FU6" s="2"/>
+      <c r="FV6" s="2"/>
+      <c r="FW6" s="5"/>
+      <c r="FX6" s="2"/>
+      <c r="FY6" s="13"/>
+      <c r="FZ6" s="2"/>
+      <c r="GA6" s="13"/>
+      <c r="GB6" s="5"/>
+      <c r="GC6" s="2"/>
+      <c r="GD6" s="2"/>
+      <c r="GE6" s="2"/>
+      <c r="GF6" s="13"/>
+      <c r="GG6" s="2"/>
+      <c r="GH6" s="2"/>
     </row>
-    <row r="7" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7"/>
       <c r="D7" s="11"/>
       <c r="E7" s="1"/>
@@ -4169,46 +4607,37 @@
       <c r="AE7" s="12"/>
       <c r="AL7" s="12"/>
       <c r="AV7" s="12"/>
-      <c r="BO7" s="5"/>
       <c r="BP7" s="5"/>
-      <c r="BQ7" s="2"/>
-      <c r="BR7" s="5"/>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2"/>
+      <c r="BQ7" s="5"/>
+      <c r="BR7" s="2"/>
+      <c r="BT7" s="5"/>
       <c r="BU7" s="2"/>
       <c r="BV7" s="2"/>
-      <c r="BX7" s="5"/>
-      <c r="BY7" s="2"/>
-      <c r="BZ7" s="5"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2"/>
       <c r="CA7" s="5"/>
       <c r="CB7" s="2"/>
-      <c r="CC7" s="2"/>
+      <c r="CC7" s="5"/>
       <c r="CD7" s="5"/>
       <c r="CE7" s="2"/>
       <c r="CF7" s="2"/>
-      <c r="CG7" s="2"/>
-      <c r="CH7" s="2"/>
+      <c r="CH7" s="5"/>
       <c r="CI7" s="2"/>
-      <c r="CJ7" s="5"/>
-      <c r="CK7" s="5"/>
+      <c r="CJ7" s="2"/>
+      <c r="CK7" s="2"/>
       <c r="CL7" s="2"/>
       <c r="CM7" s="2"/>
       <c r="CN7" s="5"/>
-      <c r="CO7" s="5"/>
-      <c r="CP7" s="2"/>
-      <c r="CQ7" s="5"/>
-      <c r="CR7" s="5"/>
-      <c r="CS7" s="2"/>
-      <c r="CT7" s="2"/>
-      <c r="CU7" s="2"/>
+      <c r="CP7" s="5"/>
+      <c r="CQ7" s="2"/>
+      <c r="CR7" s="2"/>
+      <c r="CS7" s="5"/>
+      <c r="CU7" s="5"/>
       <c r="CV7" s="2"/>
-      <c r="CW7" s="2"/>
-      <c r="CX7" s="2"/>
-      <c r="CY7" s="2"/>
-      <c r="CZ7" s="2"/>
+      <c r="CX7" s="5"/>
+      <c r="CY7" s="5"/>
       <c r="DA7" s="2"/>
-      <c r="DB7" s="2"/>
-      <c r="DC7" s="5"/>
+      <c r="DC7" s="2"/>
       <c r="DD7" s="2"/>
       <c r="DE7" s="2"/>
       <c r="DF7" s="2"/>
@@ -4217,56 +4646,71 @@
       <c r="DI7" s="2"/>
       <c r="DJ7" s="2"/>
       <c r="DK7" s="2"/>
-      <c r="DL7" s="2"/>
-      <c r="DM7" s="2"/>
+      <c r="DL7" s="5"/>
       <c r="DN7" s="2"/>
       <c r="DO7" s="2"/>
-      <c r="DP7" s="2"/>
       <c r="DQ7" s="2"/>
       <c r="DR7" s="2"/>
-      <c r="DS7" s="2"/>
       <c r="DT7" s="2"/>
       <c r="DU7" s="2"/>
       <c r="DV7" s="2"/>
       <c r="DW7" s="2"/>
-      <c r="DX7" s="10"/>
-      <c r="DY7" s="5"/>
-      <c r="DZ7" s="5"/>
-      <c r="EA7" s="5"/>
-      <c r="EB7" s="5"/>
-      <c r="EC7" s="5"/>
+      <c r="DX7" s="2"/>
+      <c r="DY7" s="2"/>
+      <c r="EA7" s="2"/>
+      <c r="EC7" s="2"/>
       <c r="ED7" s="2"/>
       <c r="EE7" s="2"/>
-      <c r="EF7" s="5"/>
-      <c r="EG7" s="5"/>
+      <c r="EF7" s="2"/>
       <c r="EH7" s="2"/>
       <c r="EI7" s="2"/>
-      <c r="EJ7" s="2"/>
       <c r="EK7" s="2"/>
-      <c r="EL7" s="5"/>
+      <c r="EL7" s="2"/>
       <c r="EM7" s="2"/>
-      <c r="EN7" s="2"/>
-      <c r="EO7" s="5"/>
-      <c r="EP7" s="2"/>
-      <c r="EQ7" s="2"/>
+      <c r="EO7" s="10"/>
+      <c r="EP7" s="5"/>
+      <c r="EQ7" s="5"/>
       <c r="ER7" s="5"/>
-      <c r="ES7" s="5"/>
-      <c r="ET7" s="2"/>
-      <c r="EU7" s="2"/>
-      <c r="EV7" s="2"/>
+      <c r="ET7" s="5"/>
+      <c r="EU7" s="5"/>
+      <c r="EV7" s="13"/>
       <c r="EW7" s="2"/>
       <c r="EX7" s="2"/>
       <c r="EY7" s="5"/>
-      <c r="EZ7" s="2"/>
-      <c r="FA7" s="2"/>
-      <c r="FB7" s="5"/>
+      <c r="EZ7" s="13"/>
+      <c r="FA7" s="5"/>
+      <c r="FB7" s="2"/>
       <c r="FC7" s="2"/>
       <c r="FD7" s="2"/>
       <c r="FE7" s="2"/>
-      <c r="FF7" s="2"/>
-      <c r="FG7" s="2"/>
+      <c r="FF7" s="13"/>
+      <c r="FG7" s="5"/>
+      <c r="FH7" s="2"/>
+      <c r="FJ7" s="2"/>
+      <c r="FK7" s="5"/>
+      <c r="FM7" s="2"/>
+      <c r="FN7" s="2"/>
+      <c r="FO7" s="5"/>
+      <c r="FQ7" s="5"/>
+      <c r="FR7" s="2"/>
+      <c r="FS7" s="2"/>
+      <c r="FT7" s="2"/>
+      <c r="FU7" s="2"/>
+      <c r="FV7" s="2"/>
+      <c r="FW7" s="5"/>
+      <c r="FX7" s="2"/>
+      <c r="FY7" s="13"/>
+      <c r="FZ7" s="2"/>
+      <c r="GA7" s="13"/>
+      <c r="GB7" s="5"/>
+      <c r="GC7" s="2"/>
+      <c r="GD7" s="2"/>
+      <c r="GE7" s="2"/>
+      <c r="GF7" s="13"/>
+      <c r="GG7" s="2"/>
+      <c r="GH7" s="2"/>
     </row>
-    <row r="8" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8"/>
       <c r="D8" s="11"/>
       <c r="E8" s="1"/>
@@ -4281,46 +4725,37 @@
       <c r="AE8" s="12"/>
       <c r="AL8" s="12"/>
       <c r="AV8" s="12"/>
-      <c r="BO8" s="5"/>
       <c r="BP8" s="5"/>
-      <c r="BQ8" s="2"/>
-      <c r="BR8" s="5"/>
-      <c r="BS8" s="2"/>
-      <c r="BT8" s="2"/>
+      <c r="BQ8" s="5"/>
+      <c r="BR8" s="2"/>
+      <c r="BT8" s="5"/>
       <c r="BU8" s="2"/>
       <c r="BV8" s="2"/>
-      <c r="BX8" s="5"/>
-      <c r="BY8" s="2"/>
-      <c r="BZ8" s="5"/>
+      <c r="BW8" s="2"/>
+      <c r="BX8" s="2"/>
       <c r="CA8" s="5"/>
       <c r="CB8" s="2"/>
-      <c r="CC8" s="2"/>
+      <c r="CC8" s="5"/>
       <c r="CD8" s="5"/>
       <c r="CE8" s="2"/>
       <c r="CF8" s="2"/>
-      <c r="CG8" s="2"/>
-      <c r="CH8" s="2"/>
+      <c r="CH8" s="5"/>
       <c r="CI8" s="2"/>
-      <c r="CJ8" s="5"/>
-      <c r="CK8" s="5"/>
+      <c r="CJ8" s="2"/>
+      <c r="CK8" s="2"/>
       <c r="CL8" s="2"/>
       <c r="CM8" s="2"/>
       <c r="CN8" s="5"/>
-      <c r="CO8" s="5"/>
-      <c r="CP8" s="2"/>
-      <c r="CQ8" s="5"/>
-      <c r="CR8" s="5"/>
-      <c r="CS8" s="2"/>
-      <c r="CT8" s="2"/>
-      <c r="CU8" s="2"/>
+      <c r="CP8" s="5"/>
+      <c r="CQ8" s="2"/>
+      <c r="CR8" s="2"/>
+      <c r="CS8" s="5"/>
+      <c r="CU8" s="5"/>
       <c r="CV8" s="2"/>
-      <c r="CW8" s="2"/>
-      <c r="CX8" s="2"/>
-      <c r="CY8" s="2"/>
-      <c r="CZ8" s="2"/>
+      <c r="CX8" s="5"/>
+      <c r="CY8" s="5"/>
       <c r="DA8" s="2"/>
-      <c r="DB8" s="2"/>
-      <c r="DC8" s="5"/>
+      <c r="DC8" s="2"/>
       <c r="DD8" s="2"/>
       <c r="DE8" s="2"/>
       <c r="DF8" s="2"/>
@@ -4329,56 +4764,71 @@
       <c r="DI8" s="2"/>
       <c r="DJ8" s="2"/>
       <c r="DK8" s="2"/>
-      <c r="DL8" s="2"/>
-      <c r="DM8" s="2"/>
+      <c r="DL8" s="5"/>
       <c r="DN8" s="2"/>
       <c r="DO8" s="2"/>
-      <c r="DP8" s="2"/>
       <c r="DQ8" s="2"/>
       <c r="DR8" s="2"/>
-      <c r="DS8" s="2"/>
       <c r="DT8" s="2"/>
       <c r="DU8" s="2"/>
       <c r="DV8" s="2"/>
       <c r="DW8" s="2"/>
-      <c r="DX8" s="10"/>
-      <c r="DY8" s="5"/>
-      <c r="DZ8" s="5"/>
-      <c r="EA8" s="5"/>
-      <c r="EB8" s="5"/>
-      <c r="EC8" s="5"/>
+      <c r="DX8" s="2"/>
+      <c r="DY8" s="2"/>
+      <c r="EA8" s="2"/>
+      <c r="EC8" s="2"/>
       <c r="ED8" s="2"/>
       <c r="EE8" s="2"/>
-      <c r="EF8" s="5"/>
-      <c r="EG8" s="5"/>
+      <c r="EF8" s="2"/>
       <c r="EH8" s="2"/>
       <c r="EI8" s="2"/>
-      <c r="EJ8" s="2"/>
       <c r="EK8" s="2"/>
-      <c r="EL8" s="5"/>
+      <c r="EL8" s="2"/>
       <c r="EM8" s="2"/>
-      <c r="EN8" s="2"/>
-      <c r="EO8" s="5"/>
-      <c r="EP8" s="2"/>
-      <c r="EQ8" s="2"/>
+      <c r="EO8" s="10"/>
+      <c r="EP8" s="5"/>
+      <c r="EQ8" s="5"/>
       <c r="ER8" s="5"/>
-      <c r="ES8" s="5"/>
-      <c r="ET8" s="2"/>
-      <c r="EU8" s="2"/>
-      <c r="EV8" s="2"/>
+      <c r="ET8" s="5"/>
+      <c r="EU8" s="5"/>
+      <c r="EV8" s="13"/>
       <c r="EW8" s="2"/>
       <c r="EX8" s="2"/>
       <c r="EY8" s="5"/>
-      <c r="EZ8" s="2"/>
-      <c r="FA8" s="2"/>
-      <c r="FB8" s="5"/>
+      <c r="EZ8" s="13"/>
+      <c r="FA8" s="5"/>
+      <c r="FB8" s="2"/>
       <c r="FC8" s="2"/>
       <c r="FD8" s="2"/>
       <c r="FE8" s="2"/>
-      <c r="FF8" s="2"/>
-      <c r="FG8" s="2"/>
+      <c r="FF8" s="13"/>
+      <c r="FG8" s="5"/>
+      <c r="FH8" s="2"/>
+      <c r="FJ8" s="2"/>
+      <c r="FK8" s="5"/>
+      <c r="FM8" s="2"/>
+      <c r="FN8" s="2"/>
+      <c r="FO8" s="5"/>
+      <c r="FQ8" s="5"/>
+      <c r="FR8" s="2"/>
+      <c r="FS8" s="2"/>
+      <c r="FT8" s="2"/>
+      <c r="FU8" s="2"/>
+      <c r="FV8" s="2"/>
+      <c r="FW8" s="5"/>
+      <c r="FX8" s="2"/>
+      <c r="FY8" s="13"/>
+      <c r="FZ8" s="2"/>
+      <c r="GA8" s="13"/>
+      <c r="GB8" s="5"/>
+      <c r="GC8" s="2"/>
+      <c r="GD8" s="2"/>
+      <c r="GE8" s="2"/>
+      <c r="GF8" s="13"/>
+      <c r="GG8" s="2"/>
+      <c r="GH8" s="2"/>
     </row>
-    <row r="9" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9"/>
       <c r="D9" s="11"/>
       <c r="E9" s="1"/>
@@ -4393,46 +4843,37 @@
       <c r="AE9" s="12"/>
       <c r="AL9" s="12"/>
       <c r="AV9" s="12"/>
-      <c r="BO9" s="5"/>
       <c r="BP9" s="5"/>
-      <c r="BQ9" s="2"/>
-      <c r="BR9" s="5"/>
-      <c r="BS9" s="2"/>
-      <c r="BT9" s="2"/>
+      <c r="BQ9" s="5"/>
+      <c r="BR9" s="2"/>
+      <c r="BT9" s="5"/>
       <c r="BU9" s="2"/>
       <c r="BV9" s="2"/>
-      <c r="BX9" s="5"/>
-      <c r="BY9" s="2"/>
-      <c r="BZ9" s="5"/>
+      <c r="BW9" s="2"/>
+      <c r="BX9" s="2"/>
       <c r="CA9" s="5"/>
       <c r="CB9" s="2"/>
-      <c r="CC9" s="2"/>
+      <c r="CC9" s="5"/>
       <c r="CD9" s="5"/>
       <c r="CE9" s="2"/>
       <c r="CF9" s="2"/>
-      <c r="CG9" s="2"/>
-      <c r="CH9" s="2"/>
+      <c r="CH9" s="5"/>
       <c r="CI9" s="2"/>
-      <c r="CJ9" s="5"/>
-      <c r="CK9" s="5"/>
+      <c r="CJ9" s="2"/>
+      <c r="CK9" s="2"/>
       <c r="CL9" s="2"/>
       <c r="CM9" s="2"/>
       <c r="CN9" s="5"/>
-      <c r="CO9" s="5"/>
-      <c r="CP9" s="2"/>
-      <c r="CQ9" s="5"/>
-      <c r="CR9" s="5"/>
-      <c r="CS9" s="2"/>
-      <c r="CT9" s="2"/>
-      <c r="CU9" s="2"/>
+      <c r="CP9" s="5"/>
+      <c r="CQ9" s="2"/>
+      <c r="CR9" s="2"/>
+      <c r="CS9" s="5"/>
+      <c r="CU9" s="5"/>
       <c r="CV9" s="2"/>
-      <c r="CW9" s="2"/>
-      <c r="CX9" s="2"/>
-      <c r="CY9" s="2"/>
-      <c r="CZ9" s="2"/>
+      <c r="CX9" s="5"/>
+      <c r="CY9" s="5"/>
       <c r="DA9" s="2"/>
-      <c r="DB9" s="2"/>
-      <c r="DC9" s="5"/>
+      <c r="DC9" s="2"/>
       <c r="DD9" s="2"/>
       <c r="DE9" s="2"/>
       <c r="DF9" s="2"/>
@@ -4441,56 +4882,71 @@
       <c r="DI9" s="2"/>
       <c r="DJ9" s="2"/>
       <c r="DK9" s="2"/>
-      <c r="DL9" s="2"/>
-      <c r="DM9" s="2"/>
+      <c r="DL9" s="5"/>
       <c r="DN9" s="2"/>
       <c r="DO9" s="2"/>
-      <c r="DP9" s="2"/>
       <c r="DQ9" s="2"/>
       <c r="DR9" s="2"/>
-      <c r="DS9" s="2"/>
       <c r="DT9" s="2"/>
       <c r="DU9" s="2"/>
       <c r="DV9" s="2"/>
       <c r="DW9" s="2"/>
-      <c r="DX9" s="10"/>
-      <c r="DY9" s="5"/>
-      <c r="DZ9" s="5"/>
-      <c r="EA9" s="5"/>
-      <c r="EB9" s="5"/>
-      <c r="EC9" s="5"/>
+      <c r="DX9" s="2"/>
+      <c r="DY9" s="2"/>
+      <c r="EA9" s="2"/>
+      <c r="EC9" s="2"/>
       <c r="ED9" s="2"/>
       <c r="EE9" s="2"/>
-      <c r="EF9" s="5"/>
-      <c r="EG9" s="5"/>
+      <c r="EF9" s="2"/>
       <c r="EH9" s="2"/>
       <c r="EI9" s="2"/>
-      <c r="EJ9" s="2"/>
       <c r="EK9" s="2"/>
-      <c r="EL9" s="5"/>
+      <c r="EL9" s="2"/>
       <c r="EM9" s="2"/>
-      <c r="EN9" s="2"/>
-      <c r="EO9" s="5"/>
-      <c r="EP9" s="2"/>
-      <c r="EQ9" s="2"/>
+      <c r="EO9" s="10"/>
+      <c r="EP9" s="5"/>
+      <c r="EQ9" s="5"/>
       <c r="ER9" s="5"/>
-      <c r="ES9" s="5"/>
-      <c r="ET9" s="2"/>
-      <c r="EU9" s="2"/>
-      <c r="EV9" s="2"/>
+      <c r="ET9" s="5"/>
+      <c r="EU9" s="5"/>
+      <c r="EV9" s="13"/>
       <c r="EW9" s="2"/>
       <c r="EX9" s="2"/>
       <c r="EY9" s="5"/>
-      <c r="EZ9" s="2"/>
-      <c r="FA9" s="2"/>
-      <c r="FB9" s="5"/>
+      <c r="EZ9" s="13"/>
+      <c r="FA9" s="5"/>
+      <c r="FB9" s="2"/>
       <c r="FC9" s="2"/>
       <c r="FD9" s="2"/>
       <c r="FE9" s="2"/>
-      <c r="FF9" s="2"/>
-      <c r="FG9" s="2"/>
+      <c r="FF9" s="13"/>
+      <c r="FG9" s="5"/>
+      <c r="FH9" s="2"/>
+      <c r="FJ9" s="2"/>
+      <c r="FK9" s="5"/>
+      <c r="FM9" s="2"/>
+      <c r="FN9" s="2"/>
+      <c r="FO9" s="5"/>
+      <c r="FQ9" s="5"/>
+      <c r="FR9" s="2"/>
+      <c r="FS9" s="2"/>
+      <c r="FT9" s="2"/>
+      <c r="FU9" s="2"/>
+      <c r="FV9" s="2"/>
+      <c r="FW9" s="5"/>
+      <c r="FX9" s="2"/>
+      <c r="FY9" s="13"/>
+      <c r="FZ9" s="2"/>
+      <c r="GA9" s="13"/>
+      <c r="GB9" s="5"/>
+      <c r="GC9" s="2"/>
+      <c r="GD9" s="2"/>
+      <c r="GE9" s="2"/>
+      <c r="GF9" s="13"/>
+      <c r="GG9" s="2"/>
+      <c r="GH9" s="2"/>
     </row>
-    <row r="10" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10"/>
       <c r="D10" s="11"/>
       <c r="E10" s="1"/>
@@ -4505,46 +4961,37 @@
       <c r="AE10" s="12"/>
       <c r="AL10" s="12"/>
       <c r="AV10" s="12"/>
-      <c r="BO10" s="5"/>
       <c r="BP10" s="5"/>
-      <c r="BQ10" s="2"/>
-      <c r="BR10" s="5"/>
-      <c r="BS10" s="2"/>
-      <c r="BT10" s="2"/>
+      <c r="BQ10" s="5"/>
+      <c r="BR10" s="2"/>
+      <c r="BT10" s="5"/>
       <c r="BU10" s="2"/>
       <c r="BV10" s="2"/>
-      <c r="BX10" s="5"/>
-      <c r="BY10" s="2"/>
-      <c r="BZ10" s="5"/>
+      <c r="BW10" s="2"/>
+      <c r="BX10" s="2"/>
       <c r="CA10" s="5"/>
       <c r="CB10" s="2"/>
-      <c r="CC10" s="2"/>
+      <c r="CC10" s="5"/>
       <c r="CD10" s="5"/>
       <c r="CE10" s="2"/>
       <c r="CF10" s="2"/>
-      <c r="CG10" s="2"/>
-      <c r="CH10" s="2"/>
+      <c r="CH10" s="5"/>
       <c r="CI10" s="2"/>
-      <c r="CJ10" s="5"/>
-      <c r="CK10" s="5"/>
+      <c r="CJ10" s="2"/>
+      <c r="CK10" s="2"/>
       <c r="CL10" s="2"/>
       <c r="CM10" s="2"/>
       <c r="CN10" s="5"/>
-      <c r="CO10" s="5"/>
-      <c r="CP10" s="2"/>
-      <c r="CQ10" s="5"/>
-      <c r="CR10" s="5"/>
-      <c r="CS10" s="2"/>
-      <c r="CT10" s="2"/>
-      <c r="CU10" s="2"/>
+      <c r="CP10" s="5"/>
+      <c r="CQ10" s="2"/>
+      <c r="CR10" s="2"/>
+      <c r="CS10" s="5"/>
+      <c r="CU10" s="5"/>
       <c r="CV10" s="2"/>
-      <c r="CW10" s="2"/>
-      <c r="CX10" s="2"/>
-      <c r="CY10" s="2"/>
-      <c r="CZ10" s="2"/>
+      <c r="CX10" s="5"/>
+      <c r="CY10" s="5"/>
       <c r="DA10" s="2"/>
-      <c r="DB10" s="2"/>
-      <c r="DC10" s="5"/>
+      <c r="DC10" s="2"/>
       <c r="DD10" s="2"/>
       <c r="DE10" s="2"/>
       <c r="DF10" s="2"/>
@@ -4553,56 +5000,71 @@
       <c r="DI10" s="2"/>
       <c r="DJ10" s="2"/>
       <c r="DK10" s="2"/>
-      <c r="DL10" s="2"/>
-      <c r="DM10" s="2"/>
+      <c r="DL10" s="5"/>
       <c r="DN10" s="2"/>
       <c r="DO10" s="2"/>
-      <c r="DP10" s="2"/>
       <c r="DQ10" s="2"/>
       <c r="DR10" s="2"/>
-      <c r="DS10" s="2"/>
       <c r="DT10" s="2"/>
       <c r="DU10" s="2"/>
       <c r="DV10" s="2"/>
       <c r="DW10" s="2"/>
-      <c r="DX10" s="10"/>
-      <c r="DY10" s="5"/>
-      <c r="DZ10" s="5"/>
-      <c r="EA10" s="5"/>
-      <c r="EB10" s="5"/>
-      <c r="EC10" s="5"/>
+      <c r="DX10" s="2"/>
+      <c r="DY10" s="2"/>
+      <c r="EA10" s="2"/>
+      <c r="EC10" s="2"/>
       <c r="ED10" s="2"/>
       <c r="EE10" s="2"/>
-      <c r="EF10" s="5"/>
-      <c r="EG10" s="5"/>
+      <c r="EF10" s="2"/>
       <c r="EH10" s="2"/>
       <c r="EI10" s="2"/>
-      <c r="EJ10" s="2"/>
       <c r="EK10" s="2"/>
-      <c r="EL10" s="5"/>
+      <c r="EL10" s="2"/>
       <c r="EM10" s="2"/>
-      <c r="EN10" s="2"/>
-      <c r="EO10" s="5"/>
-      <c r="EP10" s="2"/>
-      <c r="EQ10" s="2"/>
+      <c r="EO10" s="10"/>
+      <c r="EP10" s="5"/>
+      <c r="EQ10" s="5"/>
       <c r="ER10" s="5"/>
-      <c r="ES10" s="5"/>
-      <c r="ET10" s="2"/>
-      <c r="EU10" s="2"/>
-      <c r="EV10" s="2"/>
+      <c r="ET10" s="5"/>
+      <c r="EU10" s="5"/>
+      <c r="EV10" s="13"/>
       <c r="EW10" s="2"/>
       <c r="EX10" s="2"/>
       <c r="EY10" s="5"/>
-      <c r="EZ10" s="2"/>
-      <c r="FA10" s="2"/>
-      <c r="FB10" s="5"/>
+      <c r="EZ10" s="13"/>
+      <c r="FA10" s="5"/>
+      <c r="FB10" s="2"/>
       <c r="FC10" s="2"/>
       <c r="FD10" s="2"/>
       <c r="FE10" s="2"/>
-      <c r="FF10" s="2"/>
-      <c r="FG10" s="2"/>
+      <c r="FF10" s="13"/>
+      <c r="FG10" s="5"/>
+      <c r="FH10" s="2"/>
+      <c r="FJ10" s="2"/>
+      <c r="FK10" s="5"/>
+      <c r="FM10" s="2"/>
+      <c r="FN10" s="2"/>
+      <c r="FO10" s="5"/>
+      <c r="FQ10" s="5"/>
+      <c r="FR10" s="2"/>
+      <c r="FS10" s="2"/>
+      <c r="FT10" s="2"/>
+      <c r="FU10" s="2"/>
+      <c r="FV10" s="2"/>
+      <c r="FW10" s="5"/>
+      <c r="FX10" s="2"/>
+      <c r="FY10" s="13"/>
+      <c r="FZ10" s="2"/>
+      <c r="GA10" s="13"/>
+      <c r="GB10" s="5"/>
+      <c r="GC10" s="2"/>
+      <c r="GD10" s="2"/>
+      <c r="GE10" s="2"/>
+      <c r="GF10" s="13"/>
+      <c r="GG10" s="2"/>
+      <c r="GH10" s="2"/>
     </row>
-    <row r="11" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="1"/>
@@ -4617,46 +5079,37 @@
       <c r="AE11" s="12"/>
       <c r="AL11" s="12"/>
       <c r="AV11" s="12"/>
-      <c r="BO11" s="5"/>
       <c r="BP11" s="5"/>
-      <c r="BQ11" s="2"/>
-      <c r="BR11" s="5"/>
-      <c r="BS11" s="2"/>
-      <c r="BT11" s="2"/>
+      <c r="BQ11" s="5"/>
+      <c r="BR11" s="2"/>
+      <c r="BT11" s="5"/>
       <c r="BU11" s="2"/>
       <c r="BV11" s="2"/>
-      <c r="BX11" s="5"/>
-      <c r="BY11" s="2"/>
-      <c r="BZ11" s="5"/>
+      <c r="BW11" s="2"/>
+      <c r="BX11" s="2"/>
       <c r="CA11" s="5"/>
       <c r="CB11" s="2"/>
-      <c r="CC11" s="2"/>
+      <c r="CC11" s="5"/>
       <c r="CD11" s="5"/>
       <c r="CE11" s="2"/>
       <c r="CF11" s="2"/>
-      <c r="CG11" s="2"/>
-      <c r="CH11" s="2"/>
+      <c r="CH11" s="5"/>
       <c r="CI11" s="2"/>
-      <c r="CJ11" s="5"/>
-      <c r="CK11" s="5"/>
+      <c r="CJ11" s="2"/>
+      <c r="CK11" s="2"/>
       <c r="CL11" s="2"/>
       <c r="CM11" s="2"/>
       <c r="CN11" s="5"/>
-      <c r="CO11" s="5"/>
-      <c r="CP11" s="2"/>
-      <c r="CQ11" s="5"/>
-      <c r="CR11" s="5"/>
-      <c r="CS11" s="2"/>
-      <c r="CT11" s="2"/>
-      <c r="CU11" s="2"/>
+      <c r="CP11" s="5"/>
+      <c r="CQ11" s="2"/>
+      <c r="CR11" s="2"/>
+      <c r="CS11" s="5"/>
+      <c r="CU11" s="5"/>
       <c r="CV11" s="2"/>
-      <c r="CW11" s="2"/>
-      <c r="CX11" s="2"/>
-      <c r="CY11" s="2"/>
-      <c r="CZ11" s="2"/>
+      <c r="CX11" s="5"/>
+      <c r="CY11" s="5"/>
       <c r="DA11" s="2"/>
-      <c r="DB11" s="2"/>
-      <c r="DC11" s="5"/>
+      <c r="DC11" s="2"/>
       <c r="DD11" s="2"/>
       <c r="DE11" s="2"/>
       <c r="DF11" s="2"/>
@@ -4665,56 +5118,71 @@
       <c r="DI11" s="2"/>
       <c r="DJ11" s="2"/>
       <c r="DK11" s="2"/>
-      <c r="DL11" s="2"/>
-      <c r="DM11" s="2"/>
+      <c r="DL11" s="5"/>
       <c r="DN11" s="2"/>
       <c r="DO11" s="2"/>
-      <c r="DP11" s="2"/>
       <c r="DQ11" s="2"/>
       <c r="DR11" s="2"/>
-      <c r="DS11" s="2"/>
       <c r="DT11" s="2"/>
       <c r="DU11" s="2"/>
       <c r="DV11" s="2"/>
       <c r="DW11" s="2"/>
-      <c r="DX11" s="10"/>
-      <c r="DY11" s="5"/>
-      <c r="DZ11" s="5"/>
-      <c r="EA11" s="5"/>
-      <c r="EB11" s="5"/>
-      <c r="EC11" s="5"/>
+      <c r="DX11" s="2"/>
+      <c r="DY11" s="2"/>
+      <c r="EA11" s="2"/>
+      <c r="EC11" s="2"/>
       <c r="ED11" s="2"/>
       <c r="EE11" s="2"/>
-      <c r="EF11" s="5"/>
-      <c r="EG11" s="5"/>
+      <c r="EF11" s="2"/>
       <c r="EH11" s="2"/>
       <c r="EI11" s="2"/>
-      <c r="EJ11" s="2"/>
       <c r="EK11" s="2"/>
-      <c r="EL11" s="5"/>
+      <c r="EL11" s="2"/>
       <c r="EM11" s="2"/>
-      <c r="EN11" s="2"/>
-      <c r="EO11" s="5"/>
-      <c r="EP11" s="2"/>
-      <c r="EQ11" s="2"/>
+      <c r="EO11" s="10"/>
+      <c r="EP11" s="5"/>
+      <c r="EQ11" s="5"/>
       <c r="ER11" s="5"/>
-      <c r="ES11" s="5"/>
-      <c r="ET11" s="2"/>
-      <c r="EU11" s="2"/>
-      <c r="EV11" s="2"/>
+      <c r="ET11" s="5"/>
+      <c r="EU11" s="5"/>
+      <c r="EV11" s="13"/>
       <c r="EW11" s="2"/>
       <c r="EX11" s="2"/>
       <c r="EY11" s="5"/>
-      <c r="EZ11" s="2"/>
-      <c r="FA11" s="2"/>
-      <c r="FB11" s="5"/>
+      <c r="EZ11" s="13"/>
+      <c r="FA11" s="5"/>
+      <c r="FB11" s="2"/>
       <c r="FC11" s="2"/>
       <c r="FD11" s="2"/>
       <c r="FE11" s="2"/>
-      <c r="FF11" s="2"/>
-      <c r="FG11" s="2"/>
+      <c r="FF11" s="13"/>
+      <c r="FG11" s="5"/>
+      <c r="FH11" s="2"/>
+      <c r="FJ11" s="2"/>
+      <c r="FK11" s="5"/>
+      <c r="FM11" s="2"/>
+      <c r="FN11" s="2"/>
+      <c r="FO11" s="5"/>
+      <c r="FQ11" s="5"/>
+      <c r="FR11" s="2"/>
+      <c r="FS11" s="2"/>
+      <c r="FT11" s="2"/>
+      <c r="FU11" s="2"/>
+      <c r="FV11" s="2"/>
+      <c r="FW11" s="5"/>
+      <c r="FX11" s="2"/>
+      <c r="FY11" s="13"/>
+      <c r="FZ11" s="2"/>
+      <c r="GA11" s="13"/>
+      <c r="GB11" s="5"/>
+      <c r="GC11" s="2"/>
+      <c r="GD11" s="2"/>
+      <c r="GE11" s="2"/>
+      <c r="GF11" s="13"/>
+      <c r="GG11" s="2"/>
+      <c r="GH11" s="2"/>
     </row>
-    <row r="12" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12"/>
       <c r="D12" s="11"/>
       <c r="E12" s="1"/>
@@ -4729,46 +5197,37 @@
       <c r="AE12" s="12"/>
       <c r="AL12" s="12"/>
       <c r="AV12" s="12"/>
-      <c r="BO12" s="5"/>
       <c r="BP12" s="5"/>
-      <c r="BQ12" s="2"/>
-      <c r="BR12" s="5"/>
-      <c r="BS12" s="2"/>
-      <c r="BT12" s="2"/>
+      <c r="BQ12" s="5"/>
+      <c r="BR12" s="2"/>
+      <c r="BT12" s="5"/>
       <c r="BU12" s="2"/>
       <c r="BV12" s="2"/>
-      <c r="BX12" s="5"/>
-      <c r="BY12" s="2"/>
-      <c r="BZ12" s="5"/>
+      <c r="BW12" s="2"/>
+      <c r="BX12" s="2"/>
       <c r="CA12" s="5"/>
       <c r="CB12" s="2"/>
-      <c r="CC12" s="2"/>
+      <c r="CC12" s="5"/>
       <c r="CD12" s="5"/>
       <c r="CE12" s="2"/>
       <c r="CF12" s="2"/>
-      <c r="CG12" s="2"/>
-      <c r="CH12" s="2"/>
+      <c r="CH12" s="5"/>
       <c r="CI12" s="2"/>
-      <c r="CJ12" s="5"/>
-      <c r="CK12" s="5"/>
+      <c r="CJ12" s="2"/>
+      <c r="CK12" s="2"/>
       <c r="CL12" s="2"/>
       <c r="CM12" s="2"/>
       <c r="CN12" s="5"/>
-      <c r="CO12" s="5"/>
-      <c r="CP12" s="2"/>
-      <c r="CQ12" s="5"/>
-      <c r="CR12" s="5"/>
-      <c r="CS12" s="2"/>
-      <c r="CT12" s="2"/>
-      <c r="CU12" s="2"/>
+      <c r="CP12" s="5"/>
+      <c r="CQ12" s="2"/>
+      <c r="CR12" s="2"/>
+      <c r="CS12" s="5"/>
+      <c r="CU12" s="5"/>
       <c r="CV12" s="2"/>
-      <c r="CW12" s="2"/>
-      <c r="CX12" s="2"/>
-      <c r="CY12" s="2"/>
-      <c r="CZ12" s="2"/>
+      <c r="CX12" s="5"/>
+      <c r="CY12" s="5"/>
       <c r="DA12" s="2"/>
-      <c r="DB12" s="2"/>
-      <c r="DC12" s="5"/>
+      <c r="DC12" s="2"/>
       <c r="DD12" s="2"/>
       <c r="DE12" s="2"/>
       <c r="DF12" s="2"/>
@@ -4777,56 +5236,71 @@
       <c r="DI12" s="2"/>
       <c r="DJ12" s="2"/>
       <c r="DK12" s="2"/>
-      <c r="DL12" s="2"/>
-      <c r="DM12" s="2"/>
+      <c r="DL12" s="5"/>
       <c r="DN12" s="2"/>
       <c r="DO12" s="2"/>
-      <c r="DP12" s="2"/>
       <c r="DQ12" s="2"/>
       <c r="DR12" s="2"/>
-      <c r="DS12" s="2"/>
       <c r="DT12" s="2"/>
       <c r="DU12" s="2"/>
       <c r="DV12" s="2"/>
       <c r="DW12" s="2"/>
-      <c r="DX12" s="10"/>
-      <c r="DY12" s="5"/>
-      <c r="DZ12" s="5"/>
-      <c r="EA12" s="5"/>
-      <c r="EB12" s="5"/>
-      <c r="EC12" s="5"/>
+      <c r="DX12" s="2"/>
+      <c r="DY12" s="2"/>
+      <c r="EA12" s="2"/>
+      <c r="EC12" s="2"/>
       <c r="ED12" s="2"/>
       <c r="EE12" s="2"/>
-      <c r="EF12" s="5"/>
-      <c r="EG12" s="5"/>
+      <c r="EF12" s="2"/>
       <c r="EH12" s="2"/>
       <c r="EI12" s="2"/>
-      <c r="EJ12" s="2"/>
       <c r="EK12" s="2"/>
-      <c r="EL12" s="5"/>
+      <c r="EL12" s="2"/>
       <c r="EM12" s="2"/>
-      <c r="EN12" s="2"/>
-      <c r="EO12" s="5"/>
-      <c r="EP12" s="2"/>
-      <c r="EQ12" s="2"/>
+      <c r="EO12" s="10"/>
+      <c r="EP12" s="5"/>
+      <c r="EQ12" s="5"/>
       <c r="ER12" s="5"/>
-      <c r="ES12" s="5"/>
-      <c r="ET12" s="2"/>
-      <c r="EU12" s="2"/>
-      <c r="EV12" s="2"/>
+      <c r="ET12" s="5"/>
+      <c r="EU12" s="5"/>
+      <c r="EV12" s="13"/>
       <c r="EW12" s="2"/>
       <c r="EX12" s="2"/>
       <c r="EY12" s="5"/>
-      <c r="EZ12" s="2"/>
-      <c r="FA12" s="2"/>
-      <c r="FB12" s="5"/>
+      <c r="EZ12" s="13"/>
+      <c r="FA12" s="5"/>
+      <c r="FB12" s="2"/>
       <c r="FC12" s="2"/>
       <c r="FD12" s="2"/>
       <c r="FE12" s="2"/>
-      <c r="FF12" s="2"/>
-      <c r="FG12" s="2"/>
+      <c r="FF12" s="13"/>
+      <c r="FG12" s="5"/>
+      <c r="FH12" s="2"/>
+      <c r="FJ12" s="2"/>
+      <c r="FK12" s="5"/>
+      <c r="FM12" s="2"/>
+      <c r="FN12" s="2"/>
+      <c r="FO12" s="5"/>
+      <c r="FQ12" s="5"/>
+      <c r="FR12" s="2"/>
+      <c r="FS12" s="2"/>
+      <c r="FT12" s="2"/>
+      <c r="FU12" s="2"/>
+      <c r="FV12" s="2"/>
+      <c r="FW12" s="5"/>
+      <c r="FX12" s="2"/>
+      <c r="FY12" s="13"/>
+      <c r="FZ12" s="2"/>
+      <c r="GA12" s="13"/>
+      <c r="GB12" s="5"/>
+      <c r="GC12" s="2"/>
+      <c r="GD12" s="2"/>
+      <c r="GE12" s="2"/>
+      <c r="GF12" s="13"/>
+      <c r="GG12" s="2"/>
+      <c r="GH12" s="2"/>
     </row>
-    <row r="13" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13"/>
       <c r="D13" s="11"/>
       <c r="E13" s="1"/>
@@ -4841,46 +5315,37 @@
       <c r="AE13" s="12"/>
       <c r="AL13" s="12"/>
       <c r="AV13" s="12"/>
-      <c r="BO13" s="5"/>
       <c r="BP13" s="5"/>
-      <c r="BQ13" s="2"/>
-      <c r="BR13" s="5"/>
-      <c r="BS13" s="2"/>
-      <c r="BT13" s="2"/>
+      <c r="BQ13" s="5"/>
+      <c r="BR13" s="2"/>
+      <c r="BT13" s="5"/>
       <c r="BU13" s="2"/>
       <c r="BV13" s="2"/>
-      <c r="BX13" s="5"/>
-      <c r="BY13" s="2"/>
-      <c r="BZ13" s="5"/>
+      <c r="BW13" s="2"/>
+      <c r="BX13" s="2"/>
       <c r="CA13" s="5"/>
       <c r="CB13" s="2"/>
-      <c r="CC13" s="2"/>
+      <c r="CC13" s="5"/>
       <c r="CD13" s="5"/>
       <c r="CE13" s="2"/>
       <c r="CF13" s="2"/>
-      <c r="CG13" s="2"/>
-      <c r="CH13" s="2"/>
+      <c r="CH13" s="5"/>
       <c r="CI13" s="2"/>
-      <c r="CJ13" s="5"/>
-      <c r="CK13" s="5"/>
+      <c r="CJ13" s="2"/>
+      <c r="CK13" s="2"/>
       <c r="CL13" s="2"/>
       <c r="CM13" s="2"/>
       <c r="CN13" s="5"/>
-      <c r="CO13" s="5"/>
-      <c r="CP13" s="2"/>
-      <c r="CQ13" s="5"/>
-      <c r="CR13" s="5"/>
-      <c r="CS13" s="2"/>
-      <c r="CT13" s="2"/>
-      <c r="CU13" s="2"/>
+      <c r="CP13" s="5"/>
+      <c r="CQ13" s="2"/>
+      <c r="CR13" s="2"/>
+      <c r="CS13" s="5"/>
+      <c r="CU13" s="5"/>
       <c r="CV13" s="2"/>
-      <c r="CW13" s="2"/>
-      <c r="CX13" s="2"/>
-      <c r="CY13" s="2"/>
-      <c r="CZ13" s="2"/>
+      <c r="CX13" s="5"/>
+      <c r="CY13" s="5"/>
       <c r="DA13" s="2"/>
-      <c r="DB13" s="2"/>
-      <c r="DC13" s="5"/>
+      <c r="DC13" s="2"/>
       <c r="DD13" s="2"/>
       <c r="DE13" s="2"/>
       <c r="DF13" s="2"/>
@@ -4889,56 +5354,71 @@
       <c r="DI13" s="2"/>
       <c r="DJ13" s="2"/>
       <c r="DK13" s="2"/>
-      <c r="DL13" s="2"/>
-      <c r="DM13" s="2"/>
+      <c r="DL13" s="5"/>
       <c r="DN13" s="2"/>
       <c r="DO13" s="2"/>
-      <c r="DP13" s="2"/>
       <c r="DQ13" s="2"/>
       <c r="DR13" s="2"/>
-      <c r="DS13" s="2"/>
       <c r="DT13" s="2"/>
       <c r="DU13" s="2"/>
       <c r="DV13" s="2"/>
       <c r="DW13" s="2"/>
-      <c r="DX13" s="10"/>
-      <c r="DY13" s="5"/>
-      <c r="DZ13" s="5"/>
-      <c r="EA13" s="5"/>
-      <c r="EB13" s="5"/>
-      <c r="EC13" s="5"/>
+      <c r="DX13" s="2"/>
+      <c r="DY13" s="2"/>
+      <c r="EA13" s="2"/>
+      <c r="EC13" s="2"/>
       <c r="ED13" s="2"/>
       <c r="EE13" s="2"/>
-      <c r="EF13" s="5"/>
-      <c r="EG13" s="5"/>
+      <c r="EF13" s="2"/>
       <c r="EH13" s="2"/>
       <c r="EI13" s="2"/>
-      <c r="EJ13" s="2"/>
       <c r="EK13" s="2"/>
-      <c r="EL13" s="5"/>
+      <c r="EL13" s="2"/>
       <c r="EM13" s="2"/>
-      <c r="EN13" s="2"/>
-      <c r="EO13" s="5"/>
-      <c r="EP13" s="2"/>
-      <c r="EQ13" s="2"/>
+      <c r="EO13" s="10"/>
+      <c r="EP13" s="5"/>
+      <c r="EQ13" s="5"/>
       <c r="ER13" s="5"/>
-      <c r="ES13" s="5"/>
-      <c r="ET13" s="2"/>
-      <c r="EU13" s="2"/>
-      <c r="EV13" s="2"/>
+      <c r="ET13" s="5"/>
+      <c r="EU13" s="5"/>
+      <c r="EV13" s="13"/>
       <c r="EW13" s="2"/>
       <c r="EX13" s="2"/>
       <c r="EY13" s="5"/>
-      <c r="EZ13" s="2"/>
-      <c r="FA13" s="2"/>
-      <c r="FB13" s="5"/>
+      <c r="EZ13" s="13"/>
+      <c r="FA13" s="5"/>
+      <c r="FB13" s="2"/>
       <c r="FC13" s="2"/>
       <c r="FD13" s="2"/>
       <c r="FE13" s="2"/>
-      <c r="FF13" s="2"/>
-      <c r="FG13" s="2"/>
+      <c r="FF13" s="13"/>
+      <c r="FG13" s="5"/>
+      <c r="FH13" s="2"/>
+      <c r="FJ13" s="2"/>
+      <c r="FK13" s="5"/>
+      <c r="FM13" s="2"/>
+      <c r="FN13" s="2"/>
+      <c r="FO13" s="5"/>
+      <c r="FQ13" s="5"/>
+      <c r="FR13" s="2"/>
+      <c r="FS13" s="2"/>
+      <c r="FT13" s="2"/>
+      <c r="FU13" s="2"/>
+      <c r="FV13" s="2"/>
+      <c r="FW13" s="5"/>
+      <c r="FX13" s="2"/>
+      <c r="FY13" s="13"/>
+      <c r="FZ13" s="2"/>
+      <c r="GA13" s="13"/>
+      <c r="GB13" s="5"/>
+      <c r="GC13" s="2"/>
+      <c r="GD13" s="2"/>
+      <c r="GE13" s="2"/>
+      <c r="GF13" s="13"/>
+      <c r="GG13" s="2"/>
+      <c r="GH13" s="2"/>
     </row>
-    <row r="14" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14"/>
       <c r="D14" s="11"/>
       <c r="E14" s="1"/>
@@ -4953,46 +5433,37 @@
       <c r="AE14" s="12"/>
       <c r="AL14" s="12"/>
       <c r="AV14" s="12"/>
-      <c r="BO14" s="5"/>
       <c r="BP14" s="5"/>
-      <c r="BQ14" s="2"/>
-      <c r="BR14" s="5"/>
-      <c r="BS14" s="2"/>
-      <c r="BT14" s="2"/>
+      <c r="BQ14" s="5"/>
+      <c r="BR14" s="2"/>
+      <c r="BT14" s="5"/>
       <c r="BU14" s="2"/>
       <c r="BV14" s="2"/>
-      <c r="BX14" s="5"/>
-      <c r="BY14" s="2"/>
-      <c r="BZ14" s="5"/>
+      <c r="BW14" s="2"/>
+      <c r="BX14" s="2"/>
       <c r="CA14" s="5"/>
       <c r="CB14" s="2"/>
-      <c r="CC14" s="2"/>
+      <c r="CC14" s="5"/>
       <c r="CD14" s="5"/>
       <c r="CE14" s="2"/>
       <c r="CF14" s="2"/>
-      <c r="CG14" s="2"/>
-      <c r="CH14" s="2"/>
+      <c r="CH14" s="5"/>
       <c r="CI14" s="2"/>
-      <c r="CJ14" s="5"/>
-      <c r="CK14" s="5"/>
+      <c r="CJ14" s="2"/>
+      <c r="CK14" s="2"/>
       <c r="CL14" s="2"/>
       <c r="CM14" s="2"/>
       <c r="CN14" s="5"/>
-      <c r="CO14" s="5"/>
-      <c r="CP14" s="2"/>
-      <c r="CQ14" s="5"/>
-      <c r="CR14" s="5"/>
-      <c r="CS14" s="2"/>
-      <c r="CT14" s="2"/>
-      <c r="CU14" s="2"/>
+      <c r="CP14" s="5"/>
+      <c r="CQ14" s="2"/>
+      <c r="CR14" s="2"/>
+      <c r="CS14" s="5"/>
+      <c r="CU14" s="5"/>
       <c r="CV14" s="2"/>
-      <c r="CW14" s="2"/>
-      <c r="CX14" s="2"/>
-      <c r="CY14" s="2"/>
-      <c r="CZ14" s="2"/>
+      <c r="CX14" s="5"/>
+      <c r="CY14" s="5"/>
       <c r="DA14" s="2"/>
-      <c r="DB14" s="2"/>
-      <c r="DC14" s="5"/>
+      <c r="DC14" s="2"/>
       <c r="DD14" s="2"/>
       <c r="DE14" s="2"/>
       <c r="DF14" s="2"/>
@@ -5001,101 +5472,107 @@
       <c r="DI14" s="2"/>
       <c r="DJ14" s="2"/>
       <c r="DK14" s="2"/>
-      <c r="DL14" s="2"/>
-      <c r="DM14" s="2"/>
+      <c r="DL14" s="5"/>
       <c r="DN14" s="2"/>
       <c r="DO14" s="2"/>
-      <c r="DP14" s="2"/>
       <c r="DQ14" s="2"/>
       <c r="DR14" s="2"/>
-      <c r="DS14" s="2"/>
       <c r="DT14" s="2"/>
       <c r="DU14" s="2"/>
       <c r="DV14" s="2"/>
       <c r="DW14" s="2"/>
-      <c r="DX14" s="10"/>
-      <c r="DY14" s="5"/>
-      <c r="DZ14" s="5"/>
-      <c r="EA14" s="5"/>
-      <c r="EB14" s="5"/>
-      <c r="EC14" s="5"/>
+      <c r="DX14" s="2"/>
+      <c r="DY14" s="2"/>
+      <c r="EA14" s="2"/>
+      <c r="EC14" s="2"/>
       <c r="ED14" s="2"/>
       <c r="EE14" s="2"/>
-      <c r="EF14" s="5"/>
-      <c r="EG14" s="5"/>
+      <c r="EF14" s="2"/>
       <c r="EH14" s="2"/>
       <c r="EI14" s="2"/>
-      <c r="EJ14" s="2"/>
       <c r="EK14" s="2"/>
-      <c r="EL14" s="5"/>
+      <c r="EL14" s="2"/>
       <c r="EM14" s="2"/>
-      <c r="EN14" s="2"/>
-      <c r="EO14" s="5"/>
-      <c r="EP14" s="2"/>
-      <c r="EQ14" s="2"/>
+      <c r="EO14" s="10"/>
+      <c r="EP14" s="5"/>
+      <c r="EQ14" s="5"/>
       <c r="ER14" s="5"/>
-      <c r="ES14" s="5"/>
-      <c r="ET14" s="2"/>
-      <c r="EU14" s="2"/>
-      <c r="EV14" s="2"/>
+      <c r="ET14" s="5"/>
+      <c r="EU14" s="5"/>
+      <c r="EV14" s="13"/>
       <c r="EW14" s="2"/>
       <c r="EX14" s="2"/>
       <c r="EY14" s="5"/>
-      <c r="EZ14" s="2"/>
-      <c r="FA14" s="2"/>
-      <c r="FB14" s="5"/>
+      <c r="EZ14" s="13"/>
+      <c r="FA14" s="5"/>
+      <c r="FB14" s="2"/>
       <c r="FC14" s="2"/>
       <c r="FD14" s="2"/>
       <c r="FE14" s="2"/>
-      <c r="FF14" s="2"/>
-      <c r="FG14" s="2"/>
+      <c r="FF14" s="13"/>
+      <c r="FG14" s="5"/>
+      <c r="FH14" s="2"/>
+      <c r="FJ14" s="2"/>
+      <c r="FK14" s="5"/>
+      <c r="FM14" s="2"/>
+      <c r="FN14" s="2"/>
+      <c r="FO14" s="5"/>
+      <c r="FQ14" s="5"/>
+      <c r="FR14" s="2"/>
+      <c r="FS14" s="2"/>
+      <c r="FT14" s="2"/>
+      <c r="FU14" s="2"/>
+      <c r="FV14" s="2"/>
+      <c r="FW14" s="5"/>
+      <c r="FX14" s="2"/>
+      <c r="FY14" s="13"/>
+      <c r="FZ14" s="2"/>
+      <c r="GA14" s="13"/>
+      <c r="GB14" s="5"/>
+      <c r="GC14" s="2"/>
+      <c r="GD14" s="2"/>
+      <c r="GE14" s="2"/>
+      <c r="GF14" s="13"/>
+      <c r="GG14" s="2"/>
+      <c r="GH14" s="2"/>
     </row>
-    <row r="15" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="K15" s="3"/>
       <c r="L15" s="12"/>
-      <c r="BO15" s="5"/>
       <c r="BP15" s="5"/>
-      <c r="BQ15" s="2"/>
-      <c r="BR15" s="5"/>
-      <c r="BS15" s="2"/>
-      <c r="BT15" s="2"/>
+      <c r="BQ15" s="5"/>
+      <c r="BR15" s="2"/>
+      <c r="BT15" s="5"/>
       <c r="BU15" s="2"/>
       <c r="BV15" s="2"/>
-      <c r="BX15" s="5"/>
-      <c r="BY15" s="2"/>
-      <c r="BZ15" s="5"/>
+      <c r="BW15" s="2"/>
+      <c r="BX15" s="2"/>
       <c r="CA15" s="5"/>
       <c r="CB15" s="2"/>
-      <c r="CC15" s="2"/>
+      <c r="CC15" s="5"/>
       <c r="CD15" s="5"/>
       <c r="CE15" s="2"/>
       <c r="CF15" s="2"/>
-      <c r="CG15" s="2"/>
-      <c r="CH15" s="2"/>
+      <c r="CH15" s="5"/>
       <c r="CI15" s="2"/>
-      <c r="CJ15" s="5"/>
-      <c r="CK15" s="5"/>
+      <c r="CJ15" s="2"/>
+      <c r="CK15" s="2"/>
       <c r="CL15" s="2"/>
       <c r="CM15" s="2"/>
       <c r="CN15" s="5"/>
-      <c r="CO15" s="5"/>
-      <c r="CP15" s="2"/>
-      <c r="CQ15" s="5"/>
-      <c r="CR15" s="5"/>
-      <c r="CS15" s="2"/>
-      <c r="CT15" s="2"/>
-      <c r="CU15" s="2"/>
+      <c r="CP15" s="5"/>
+      <c r="CQ15" s="2"/>
+      <c r="CR15" s="2"/>
+      <c r="CS15" s="5"/>
+      <c r="CU15" s="5"/>
       <c r="CV15" s="2"/>
-      <c r="CW15" s="2"/>
-      <c r="CX15" s="2"/>
-      <c r="CY15" s="2"/>
-      <c r="CZ15" s="2"/>
+      <c r="CX15" s="5"/>
+      <c r="CY15" s="5"/>
       <c r="DA15" s="2"/>
-      <c r="DB15" s="2"/>
-      <c r="DC15" s="5"/>
+      <c r="DC15" s="2"/>
       <c r="DD15" s="2"/>
       <c r="DE15" s="2"/>
       <c r="DF15" s="2"/>
@@ -5104,101 +5581,107 @@
       <c r="DI15" s="2"/>
       <c r="DJ15" s="2"/>
       <c r="DK15" s="2"/>
-      <c r="DL15" s="2"/>
-      <c r="DM15" s="2"/>
+      <c r="DL15" s="5"/>
       <c r="DN15" s="2"/>
       <c r="DO15" s="2"/>
-      <c r="DP15" s="2"/>
       <c r="DQ15" s="2"/>
       <c r="DR15" s="2"/>
-      <c r="DS15" s="2"/>
       <c r="DT15" s="2"/>
       <c r="DU15" s="2"/>
       <c r="DV15" s="2"/>
       <c r="DW15" s="2"/>
-      <c r="DX15" s="10"/>
-      <c r="DY15" s="5"/>
-      <c r="DZ15" s="5"/>
-      <c r="EA15" s="5"/>
-      <c r="EB15" s="5"/>
-      <c r="EC15" s="5"/>
+      <c r="DX15" s="2"/>
+      <c r="DY15" s="2"/>
+      <c r="EA15" s="2"/>
+      <c r="EC15" s="2"/>
       <c r="ED15" s="2"/>
       <c r="EE15" s="2"/>
-      <c r="EF15" s="5"/>
-      <c r="EG15" s="5"/>
+      <c r="EF15" s="2"/>
       <c r="EH15" s="2"/>
       <c r="EI15" s="2"/>
-      <c r="EJ15" s="2"/>
       <c r="EK15" s="2"/>
-      <c r="EL15" s="5"/>
+      <c r="EL15" s="2"/>
       <c r="EM15" s="2"/>
-      <c r="EN15" s="2"/>
-      <c r="EO15" s="5"/>
-      <c r="EP15" s="2"/>
-      <c r="EQ15" s="2"/>
+      <c r="EO15" s="10"/>
+      <c r="EP15" s="5"/>
+      <c r="EQ15" s="5"/>
       <c r="ER15" s="5"/>
-      <c r="ES15" s="5"/>
-      <c r="ET15" s="2"/>
-      <c r="EU15" s="2"/>
-      <c r="EV15" s="2"/>
+      <c r="ET15" s="5"/>
+      <c r="EU15" s="5"/>
+      <c r="EV15" s="13"/>
       <c r="EW15" s="2"/>
       <c r="EX15" s="2"/>
       <c r="EY15" s="5"/>
-      <c r="EZ15" s="2"/>
-      <c r="FA15" s="2"/>
-      <c r="FB15" s="5"/>
+      <c r="EZ15" s="13"/>
+      <c r="FA15" s="5"/>
+      <c r="FB15" s="2"/>
       <c r="FC15" s="2"/>
       <c r="FD15" s="2"/>
       <c r="FE15" s="2"/>
-      <c r="FF15" s="2"/>
-      <c r="FG15" s="2"/>
+      <c r="FF15" s="13"/>
+      <c r="FG15" s="5"/>
+      <c r="FH15" s="2"/>
+      <c r="FJ15" s="2"/>
+      <c r="FK15" s="5"/>
+      <c r="FM15" s="2"/>
+      <c r="FN15" s="2"/>
+      <c r="FO15" s="5"/>
+      <c r="FQ15" s="5"/>
+      <c r="FR15" s="2"/>
+      <c r="FS15" s="2"/>
+      <c r="FT15" s="2"/>
+      <c r="FU15" s="2"/>
+      <c r="FV15" s="2"/>
+      <c r="FW15" s="5"/>
+      <c r="FX15" s="2"/>
+      <c r="FY15" s="13"/>
+      <c r="FZ15" s="2"/>
+      <c r="GA15" s="13"/>
+      <c r="GB15" s="5"/>
+      <c r="GC15" s="2"/>
+      <c r="GD15" s="2"/>
+      <c r="GE15" s="2"/>
+      <c r="GF15" s="13"/>
+      <c r="GG15" s="2"/>
+      <c r="GH15" s="2"/>
     </row>
-    <row r="16" spans="1:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="K16" s="3"/>
       <c r="L16" s="12"/>
-      <c r="BO16" s="5"/>
       <c r="BP16" s="5"/>
-      <c r="BQ16" s="2"/>
-      <c r="BR16" s="5"/>
-      <c r="BS16" s="2"/>
-      <c r="BT16" s="2"/>
+      <c r="BQ16" s="5"/>
+      <c r="BR16" s="2"/>
+      <c r="BT16" s="5"/>
       <c r="BU16" s="2"/>
       <c r="BV16" s="2"/>
-      <c r="BX16" s="5"/>
-      <c r="BY16" s="2"/>
-      <c r="BZ16" s="5"/>
+      <c r="BW16" s="2"/>
+      <c r="BX16" s="2"/>
       <c r="CA16" s="5"/>
       <c r="CB16" s="2"/>
-      <c r="CC16" s="2"/>
+      <c r="CC16" s="5"/>
       <c r="CD16" s="5"/>
       <c r="CE16" s="2"/>
       <c r="CF16" s="2"/>
-      <c r="CG16" s="2"/>
-      <c r="CH16" s="2"/>
+      <c r="CH16" s="5"/>
       <c r="CI16" s="2"/>
-      <c r="CJ16" s="5"/>
-      <c r="CK16" s="5"/>
+      <c r="CJ16" s="2"/>
+      <c r="CK16" s="2"/>
       <c r="CL16" s="2"/>
       <c r="CM16" s="2"/>
       <c r="CN16" s="5"/>
-      <c r="CO16" s="5"/>
-      <c r="CP16" s="2"/>
-      <c r="CQ16" s="5"/>
-      <c r="CR16" s="5"/>
-      <c r="CS16" s="2"/>
-      <c r="CT16" s="2"/>
-      <c r="CU16" s="2"/>
+      <c r="CP16" s="5"/>
+      <c r="CQ16" s="2"/>
+      <c r="CR16" s="2"/>
+      <c r="CS16" s="5"/>
+      <c r="CU16" s="5"/>
       <c r="CV16" s="2"/>
-      <c r="CW16" s="2"/>
-      <c r="CX16" s="2"/>
-      <c r="CY16" s="2"/>
-      <c r="CZ16" s="2"/>
+      <c r="CX16" s="5"/>
+      <c r="CY16" s="5"/>
       <c r="DA16" s="2"/>
-      <c r="DB16" s="2"/>
-      <c r="DC16" s="5"/>
+      <c r="DC16" s="2"/>
       <c r="DD16" s="2"/>
       <c r="DE16" s="2"/>
       <c r="DF16" s="2"/>
@@ -5207,101 +5690,107 @@
       <c r="DI16" s="2"/>
       <c r="DJ16" s="2"/>
       <c r="DK16" s="2"/>
-      <c r="DL16" s="2"/>
-      <c r="DM16" s="2"/>
+      <c r="DL16" s="5"/>
       <c r="DN16" s="2"/>
       <c r="DO16" s="2"/>
-      <c r="DP16" s="2"/>
       <c r="DQ16" s="2"/>
       <c r="DR16" s="2"/>
-      <c r="DS16" s="2"/>
       <c r="DT16" s="2"/>
       <c r="DU16" s="2"/>
       <c r="DV16" s="2"/>
       <c r="DW16" s="2"/>
-      <c r="DX16" s="10"/>
-      <c r="DY16" s="5"/>
-      <c r="DZ16" s="5"/>
-      <c r="EA16" s="5"/>
-      <c r="EB16" s="5"/>
-      <c r="EC16" s="5"/>
+      <c r="DX16" s="2"/>
+      <c r="DY16" s="2"/>
+      <c r="EA16" s="2"/>
+      <c r="EC16" s="2"/>
       <c r="ED16" s="2"/>
       <c r="EE16" s="2"/>
-      <c r="EF16" s="5"/>
-      <c r="EG16" s="5"/>
+      <c r="EF16" s="2"/>
       <c r="EH16" s="2"/>
       <c r="EI16" s="2"/>
-      <c r="EJ16" s="2"/>
       <c r="EK16" s="2"/>
-      <c r="EL16" s="5"/>
+      <c r="EL16" s="2"/>
       <c r="EM16" s="2"/>
-      <c r="EN16" s="2"/>
-      <c r="EO16" s="5"/>
-      <c r="EP16" s="2"/>
-      <c r="EQ16" s="2"/>
+      <c r="EO16" s="10"/>
+      <c r="EP16" s="5"/>
+      <c r="EQ16" s="5"/>
       <c r="ER16" s="5"/>
-      <c r="ES16" s="5"/>
-      <c r="ET16" s="2"/>
-      <c r="EU16" s="2"/>
-      <c r="EV16" s="2"/>
+      <c r="ET16" s="5"/>
+      <c r="EU16" s="5"/>
+      <c r="EV16" s="13"/>
       <c r="EW16" s="2"/>
       <c r="EX16" s="2"/>
       <c r="EY16" s="5"/>
-      <c r="EZ16" s="2"/>
-      <c r="FA16" s="2"/>
-      <c r="FB16" s="5"/>
+      <c r="EZ16" s="13"/>
+      <c r="FA16" s="5"/>
+      <c r="FB16" s="2"/>
       <c r="FC16" s="2"/>
       <c r="FD16" s="2"/>
       <c r="FE16" s="2"/>
-      <c r="FF16" s="2"/>
-      <c r="FG16" s="2"/>
+      <c r="FF16" s="13"/>
+      <c r="FG16" s="5"/>
+      <c r="FH16" s="2"/>
+      <c r="FJ16" s="2"/>
+      <c r="FK16" s="5"/>
+      <c r="FM16" s="2"/>
+      <c r="FN16" s="2"/>
+      <c r="FO16" s="5"/>
+      <c r="FQ16" s="5"/>
+      <c r="FR16" s="2"/>
+      <c r="FS16" s="2"/>
+      <c r="FT16" s="2"/>
+      <c r="FU16" s="2"/>
+      <c r="FV16" s="2"/>
+      <c r="FW16" s="5"/>
+      <c r="FX16" s="2"/>
+      <c r="FY16" s="13"/>
+      <c r="FZ16" s="2"/>
+      <c r="GA16" s="13"/>
+      <c r="GB16" s="5"/>
+      <c r="GC16" s="2"/>
+      <c r="GD16" s="2"/>
+      <c r="GE16" s="2"/>
+      <c r="GF16" s="13"/>
+      <c r="GG16" s="2"/>
+      <c r="GH16" s="2"/>
     </row>
-    <row r="17" spans="5:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="5:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="K17" s="3"/>
       <c r="L17" s="12"/>
-      <c r="BO17" s="5"/>
       <c r="BP17" s="5"/>
-      <c r="BQ17" s="2"/>
-      <c r="BR17" s="5"/>
-      <c r="BS17" s="2"/>
-      <c r="BT17" s="2"/>
+      <c r="BQ17" s="5"/>
+      <c r="BR17" s="2"/>
+      <c r="BT17" s="5"/>
       <c r="BU17" s="2"/>
       <c r="BV17" s="2"/>
-      <c r="BX17" s="5"/>
-      <c r="BY17" s="2"/>
-      <c r="BZ17" s="5"/>
+      <c r="BW17" s="2"/>
+      <c r="BX17" s="2"/>
       <c r="CA17" s="5"/>
       <c r="CB17" s="2"/>
-      <c r="CC17" s="2"/>
+      <c r="CC17" s="5"/>
       <c r="CD17" s="5"/>
       <c r="CE17" s="2"/>
       <c r="CF17" s="2"/>
-      <c r="CG17" s="2"/>
-      <c r="CH17" s="2"/>
+      <c r="CH17" s="5"/>
       <c r="CI17" s="2"/>
-      <c r="CJ17" s="5"/>
-      <c r="CK17" s="5"/>
+      <c r="CJ17" s="2"/>
+      <c r="CK17" s="2"/>
       <c r="CL17" s="2"/>
       <c r="CM17" s="2"/>
       <c r="CN17" s="5"/>
-      <c r="CO17" s="5"/>
-      <c r="CP17" s="2"/>
-      <c r="CQ17" s="5"/>
-      <c r="CR17" s="5"/>
-      <c r="CS17" s="2"/>
-      <c r="CT17" s="2"/>
-      <c r="CU17" s="2"/>
+      <c r="CP17" s="5"/>
+      <c r="CQ17" s="2"/>
+      <c r="CR17" s="2"/>
+      <c r="CS17" s="5"/>
+      <c r="CU17" s="5"/>
       <c r="CV17" s="2"/>
-      <c r="CW17" s="2"/>
-      <c r="CX17" s="2"/>
-      <c r="CY17" s="2"/>
-      <c r="CZ17" s="2"/>
+      <c r="CX17" s="5"/>
+      <c r="CY17" s="5"/>
       <c r="DA17" s="2"/>
-      <c r="DB17" s="2"/>
-      <c r="DC17" s="5"/>
+      <c r="DC17" s="2"/>
       <c r="DD17" s="2"/>
       <c r="DE17" s="2"/>
       <c r="DF17" s="2"/>
@@ -5310,101 +5799,107 @@
       <c r="DI17" s="2"/>
       <c r="DJ17" s="2"/>
       <c r="DK17" s="2"/>
-      <c r="DL17" s="2"/>
-      <c r="DM17" s="2"/>
+      <c r="DL17" s="5"/>
       <c r="DN17" s="2"/>
       <c r="DO17" s="2"/>
-      <c r="DP17" s="2"/>
       <c r="DQ17" s="2"/>
       <c r="DR17" s="2"/>
-      <c r="DS17" s="2"/>
       <c r="DT17" s="2"/>
       <c r="DU17" s="2"/>
       <c r="DV17" s="2"/>
       <c r="DW17" s="2"/>
-      <c r="DX17" s="10"/>
-      <c r="DY17" s="5"/>
-      <c r="DZ17" s="5"/>
-      <c r="EA17" s="5"/>
-      <c r="EB17" s="5"/>
-      <c r="EC17" s="5"/>
+      <c r="DX17" s="2"/>
+      <c r="DY17" s="2"/>
+      <c r="EA17" s="2"/>
+      <c r="EC17" s="2"/>
       <c r="ED17" s="2"/>
       <c r="EE17" s="2"/>
-      <c r="EF17" s="5"/>
-      <c r="EG17" s="5"/>
+      <c r="EF17" s="2"/>
       <c r="EH17" s="2"/>
       <c r="EI17" s="2"/>
-      <c r="EJ17" s="2"/>
       <c r="EK17" s="2"/>
-      <c r="EL17" s="5"/>
+      <c r="EL17" s="2"/>
       <c r="EM17" s="2"/>
-      <c r="EN17" s="2"/>
-      <c r="EO17" s="5"/>
-      <c r="EP17" s="2"/>
-      <c r="EQ17" s="2"/>
+      <c r="EO17" s="10"/>
+      <c r="EP17" s="5"/>
+      <c r="EQ17" s="5"/>
       <c r="ER17" s="5"/>
-      <c r="ES17" s="5"/>
-      <c r="ET17" s="2"/>
-      <c r="EU17" s="2"/>
-      <c r="EV17" s="2"/>
+      <c r="ET17" s="5"/>
+      <c r="EU17" s="5"/>
+      <c r="EV17" s="13"/>
       <c r="EW17" s="2"/>
       <c r="EX17" s="2"/>
       <c r="EY17" s="5"/>
-      <c r="EZ17" s="2"/>
-      <c r="FA17" s="2"/>
-      <c r="FB17" s="5"/>
+      <c r="EZ17" s="13"/>
+      <c r="FA17" s="5"/>
+      <c r="FB17" s="2"/>
       <c r="FC17" s="2"/>
       <c r="FD17" s="2"/>
       <c r="FE17" s="2"/>
-      <c r="FF17" s="2"/>
-      <c r="FG17" s="2"/>
+      <c r="FF17" s="13"/>
+      <c r="FG17" s="5"/>
+      <c r="FH17" s="2"/>
+      <c r="FJ17" s="2"/>
+      <c r="FK17" s="5"/>
+      <c r="FM17" s="2"/>
+      <c r="FN17" s="2"/>
+      <c r="FO17" s="5"/>
+      <c r="FQ17" s="5"/>
+      <c r="FR17" s="2"/>
+      <c r="FS17" s="2"/>
+      <c r="FT17" s="2"/>
+      <c r="FU17" s="2"/>
+      <c r="FV17" s="2"/>
+      <c r="FW17" s="5"/>
+      <c r="FX17" s="2"/>
+      <c r="FY17" s="13"/>
+      <c r="FZ17" s="2"/>
+      <c r="GA17" s="13"/>
+      <c r="GB17" s="5"/>
+      <c r="GC17" s="2"/>
+      <c r="GD17" s="2"/>
+      <c r="GE17" s="2"/>
+      <c r="GF17" s="13"/>
+      <c r="GG17" s="2"/>
+      <c r="GH17" s="2"/>
     </row>
-    <row r="18" spans="5:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="5:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="K18" s="3"/>
       <c r="L18" s="12"/>
-      <c r="BO18" s="5"/>
       <c r="BP18" s="5"/>
-      <c r="BQ18" s="2"/>
-      <c r="BR18" s="5"/>
-      <c r="BS18" s="2"/>
-      <c r="BT18" s="2"/>
+      <c r="BQ18" s="5"/>
+      <c r="BR18" s="2"/>
+      <c r="BT18" s="5"/>
       <c r="BU18" s="2"/>
       <c r="BV18" s="2"/>
-      <c r="BX18" s="5"/>
-      <c r="BY18" s="2"/>
-      <c r="BZ18" s="5"/>
+      <c r="BW18" s="2"/>
+      <c r="BX18" s="2"/>
       <c r="CA18" s="5"/>
       <c r="CB18" s="2"/>
-      <c r="CC18" s="2"/>
+      <c r="CC18" s="5"/>
       <c r="CD18" s="5"/>
       <c r="CE18" s="2"/>
       <c r="CF18" s="2"/>
-      <c r="CG18" s="2"/>
-      <c r="CH18" s="2"/>
+      <c r="CH18" s="5"/>
       <c r="CI18" s="2"/>
-      <c r="CJ18" s="5"/>
-      <c r="CK18" s="5"/>
+      <c r="CJ18" s="2"/>
+      <c r="CK18" s="2"/>
       <c r="CL18" s="2"/>
       <c r="CM18" s="2"/>
       <c r="CN18" s="5"/>
-      <c r="CO18" s="5"/>
-      <c r="CP18" s="2"/>
-      <c r="CQ18" s="5"/>
-      <c r="CR18" s="5"/>
-      <c r="CS18" s="2"/>
-      <c r="CT18" s="2"/>
-      <c r="CU18" s="2"/>
+      <c r="CP18" s="5"/>
+      <c r="CQ18" s="2"/>
+      <c r="CR18" s="2"/>
+      <c r="CS18" s="5"/>
+      <c r="CU18" s="5"/>
       <c r="CV18" s="2"/>
-      <c r="CW18" s="2"/>
-      <c r="CX18" s="2"/>
-      <c r="CY18" s="2"/>
-      <c r="CZ18" s="2"/>
+      <c r="CX18" s="5"/>
+      <c r="CY18" s="5"/>
       <c r="DA18" s="2"/>
-      <c r="DB18" s="2"/>
-      <c r="DC18" s="5"/>
+      <c r="DC18" s="2"/>
       <c r="DD18" s="2"/>
       <c r="DE18" s="2"/>
       <c r="DF18" s="2"/>
@@ -5413,101 +5908,107 @@
       <c r="DI18" s="2"/>
       <c r="DJ18" s="2"/>
       <c r="DK18" s="2"/>
-      <c r="DL18" s="2"/>
-      <c r="DM18" s="2"/>
+      <c r="DL18" s="5"/>
       <c r="DN18" s="2"/>
       <c r="DO18" s="2"/>
-      <c r="DP18" s="2"/>
       <c r="DQ18" s="2"/>
       <c r="DR18" s="2"/>
-      <c r="DS18" s="2"/>
       <c r="DT18" s="2"/>
       <c r="DU18" s="2"/>
       <c r="DV18" s="2"/>
       <c r="DW18" s="2"/>
-      <c r="DX18" s="10"/>
-      <c r="DY18" s="5"/>
-      <c r="DZ18" s="5"/>
-      <c r="EA18" s="5"/>
-      <c r="EB18" s="5"/>
-      <c r="EC18" s="5"/>
+      <c r="DX18" s="2"/>
+      <c r="DY18" s="2"/>
+      <c r="EA18" s="2"/>
+      <c r="EC18" s="2"/>
       <c r="ED18" s="2"/>
       <c r="EE18" s="2"/>
-      <c r="EF18" s="5"/>
-      <c r="EG18" s="5"/>
+      <c r="EF18" s="2"/>
       <c r="EH18" s="2"/>
       <c r="EI18" s="2"/>
-      <c r="EJ18" s="2"/>
       <c r="EK18" s="2"/>
-      <c r="EL18" s="5"/>
+      <c r="EL18" s="2"/>
       <c r="EM18" s="2"/>
-      <c r="EN18" s="2"/>
-      <c r="EO18" s="5"/>
-      <c r="EP18" s="2"/>
-      <c r="EQ18" s="2"/>
+      <c r="EO18" s="10"/>
+      <c r="EP18" s="5"/>
+      <c r="EQ18" s="5"/>
       <c r="ER18" s="5"/>
-      <c r="ES18" s="5"/>
-      <c r="ET18" s="2"/>
-      <c r="EU18" s="2"/>
-      <c r="EV18" s="2"/>
+      <c r="ET18" s="5"/>
+      <c r="EU18" s="5"/>
+      <c r="EV18" s="13"/>
       <c r="EW18" s="2"/>
       <c r="EX18" s="2"/>
       <c r="EY18" s="5"/>
-      <c r="EZ18" s="2"/>
-      <c r="FA18" s="2"/>
-      <c r="FB18" s="5"/>
+      <c r="EZ18" s="13"/>
+      <c r="FA18" s="5"/>
+      <c r="FB18" s="2"/>
       <c r="FC18" s="2"/>
       <c r="FD18" s="2"/>
       <c r="FE18" s="2"/>
-      <c r="FF18" s="2"/>
-      <c r="FG18" s="2"/>
+      <c r="FF18" s="13"/>
+      <c r="FG18" s="5"/>
+      <c r="FH18" s="2"/>
+      <c r="FJ18" s="2"/>
+      <c r="FK18" s="5"/>
+      <c r="FM18" s="2"/>
+      <c r="FN18" s="2"/>
+      <c r="FO18" s="5"/>
+      <c r="FQ18" s="5"/>
+      <c r="FR18" s="2"/>
+      <c r="FS18" s="2"/>
+      <c r="FT18" s="2"/>
+      <c r="FU18" s="2"/>
+      <c r="FV18" s="2"/>
+      <c r="FW18" s="5"/>
+      <c r="FX18" s="2"/>
+      <c r="FY18" s="13"/>
+      <c r="FZ18" s="2"/>
+      <c r="GA18" s="13"/>
+      <c r="GB18" s="5"/>
+      <c r="GC18" s="2"/>
+      <c r="GD18" s="2"/>
+      <c r="GE18" s="2"/>
+      <c r="GF18" s="13"/>
+      <c r="GG18" s="2"/>
+      <c r="GH18" s="2"/>
     </row>
-    <row r="19" spans="5:163" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="5:190" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="K19" s="3"/>
       <c r="L19" s="12"/>
-      <c r="BO19" s="5"/>
       <c r="BP19" s="5"/>
-      <c r="BQ19" s="2"/>
-      <c r="BR19" s="5"/>
-      <c r="BS19" s="2"/>
-      <c r="BT19" s="2"/>
+      <c r="BQ19" s="5"/>
+      <c r="BR19" s="2"/>
+      <c r="BT19" s="5"/>
       <c r="BU19" s="2"/>
       <c r="BV19" s="2"/>
-      <c r="BX19" s="5"/>
-      <c r="BY19" s="2"/>
-      <c r="BZ19" s="5"/>
+      <c r="BW19" s="2"/>
+      <c r="BX19" s="2"/>
       <c r="CA19" s="5"/>
       <c r="CB19" s="2"/>
-      <c r="CC19" s="2"/>
+      <c r="CC19" s="5"/>
       <c r="CD19" s="5"/>
       <c r="CE19" s="2"/>
       <c r="CF19" s="2"/>
-      <c r="CG19" s="2"/>
-      <c r="CH19" s="2"/>
+      <c r="CH19" s="5"/>
       <c r="CI19" s="2"/>
-      <c r="CJ19" s="5"/>
-      <c r="CK19" s="5"/>
+      <c r="CJ19" s="2"/>
+      <c r="CK19" s="2"/>
       <c r="CL19" s="2"/>
       <c r="CM19" s="2"/>
       <c r="CN19" s="5"/>
-      <c r="CO19" s="5"/>
-      <c r="CP19" s="2"/>
-      <c r="CQ19" s="5"/>
-      <c r="CR19" s="5"/>
-      <c r="CS19" s="2"/>
-      <c r="CT19" s="2"/>
-      <c r="CU19" s="2"/>
+      <c r="CP19" s="5"/>
+      <c r="CQ19" s="2"/>
+      <c r="CR19" s="2"/>
+      <c r="CS19" s="5"/>
+      <c r="CU19" s="5"/>
       <c r="CV19" s="2"/>
-      <c r="CW19" s="2"/>
-      <c r="CX19" s="2"/>
-      <c r="CY19" s="2"/>
-      <c r="CZ19" s="2"/>
+      <c r="CX19" s="5"/>
+      <c r="CY19" s="5"/>
       <c r="DA19" s="2"/>
-      <c r="DB19" s="2"/>
-      <c r="DC19" s="5"/>
+      <c r="DC19" s="2"/>
       <c r="DD19" s="2"/>
       <c r="DE19" s="2"/>
       <c r="DF19" s="2"/>
@@ -5516,60 +6017,75 @@
       <c r="DI19" s="2"/>
       <c r="DJ19" s="2"/>
       <c r="DK19" s="2"/>
-      <c r="DL19" s="2"/>
-      <c r="DM19" s="2"/>
+      <c r="DL19" s="5"/>
       <c r="DN19" s="2"/>
       <c r="DO19" s="2"/>
-      <c r="DP19" s="2"/>
       <c r="DQ19" s="2"/>
       <c r="DR19" s="2"/>
-      <c r="DS19" s="2"/>
       <c r="DT19" s="2"/>
       <c r="DU19" s="2"/>
       <c r="DV19" s="2"/>
       <c r="DW19" s="2"/>
-      <c r="DX19" s="10"/>
-      <c r="DY19" s="5"/>
-      <c r="DZ19" s="5"/>
-      <c r="EA19" s="5"/>
-      <c r="EB19" s="5"/>
-      <c r="EC19" s="5"/>
+      <c r="DX19" s="2"/>
+      <c r="DY19" s="2"/>
+      <c r="EA19" s="2"/>
+      <c r="EC19" s="2"/>
       <c r="ED19" s="2"/>
       <c r="EE19" s="2"/>
-      <c r="EF19" s="5"/>
-      <c r="EG19" s="5"/>
+      <c r="EF19" s="2"/>
       <c r="EH19" s="2"/>
       <c r="EI19" s="2"/>
-      <c r="EJ19" s="2"/>
       <c r="EK19" s="2"/>
-      <c r="EL19" s="5"/>
+      <c r="EL19" s="2"/>
       <c r="EM19" s="2"/>
-      <c r="EN19" s="2"/>
-      <c r="EO19" s="5"/>
-      <c r="EP19" s="2"/>
-      <c r="EQ19" s="2"/>
+      <c r="EO19" s="10"/>
+      <c r="EP19" s="5"/>
+      <c r="EQ19" s="5"/>
       <c r="ER19" s="5"/>
-      <c r="ES19" s="5"/>
-      <c r="ET19" s="2"/>
-      <c r="EU19" s="2"/>
-      <c r="EV19" s="2"/>
+      <c r="ET19" s="5"/>
+      <c r="EU19" s="5"/>
+      <c r="EV19" s="13"/>
       <c r="EW19" s="2"/>
       <c r="EX19" s="2"/>
       <c r="EY19" s="5"/>
-      <c r="EZ19" s="2"/>
-      <c r="FA19" s="2"/>
-      <c r="FB19" s="5"/>
+      <c r="EZ19" s="13"/>
+      <c r="FA19" s="5"/>
+      <c r="FB19" s="2"/>
       <c r="FC19" s="2"/>
       <c r="FD19" s="2"/>
       <c r="FE19" s="2"/>
-      <c r="FF19" s="2"/>
+      <c r="FF19" s="13"/>
+      <c r="FG19" s="5"/>
+      <c r="FH19" s="2"/>
+      <c r="FJ19" s="2"/>
+      <c r="FK19" s="5"/>
+      <c r="FM19" s="2"/>
+      <c r="FN19" s="2"/>
+      <c r="FO19" s="5"/>
+      <c r="FQ19" s="5"/>
+      <c r="FR19" s="2"/>
+      <c r="FS19" s="2"/>
+      <c r="FT19" s="2"/>
+      <c r="FU19" s="2"/>
+      <c r="FV19" s="2"/>
+      <c r="FW19" s="5"/>
+      <c r="FX19" s="2"/>
+      <c r="FY19" s="13"/>
+      <c r="FZ19" s="2"/>
+      <c r="GA19" s="13"/>
+      <c r="GB19" s="5"/>
+      <c r="GC19" s="2"/>
+      <c r="GD19" s="2"/>
+      <c r="GE19" s="2"/>
+      <c r="GF19" s="13"/>
+      <c r="GG19" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="47">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E19" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Belum Menikah,Menikah,Cerai Mati,Cerai Hidup"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW4:AW19 AE4:AE14 N4:N14 I4:I14 J4:L19 O4:Z19 AF4:AM19 AV4:AV14 D2:D14 F2:G19 I2:L3 N2:Z3 AE2:AM3 AQ2:AQ19 AT2:AT19 AV2:AW3 AZ2:AZ19 BC2:BC19 BF2:BF19 BI2:BI19 BL2:BL19 BR2:BR19 BX2:BX19 CE2:CI19 DD2:DG19 DJ2:DM19 EH2:EK19" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW4:AW19 AE4:AE14 N4:N14 I4:I14 J4:L19 O4:Z19 AF4:AM19 AV4:AV14 D2:D14 F2:G19 I2:L3 N2:Z3 AE2:AM3 AQ2:AQ19 AT2:AT19 AV2:AW3 AZ2:AZ19 BC2:BC19 BF2:BF19 BI2:BI19 BL2:BL19 BT2:BT19 CA2:CA19 CI2:CM19 DM2:DM4 DS2:DS4 EZ2:EZ4 BO2:BO4 BS2:BS4 BZ2:BZ4 CG2:CG4 CO2:CO4 CT2:CT4 CW2:CW4 CZ2:CZ4 DB2:DB4 DN2:DO19 DP2:DP4 DQ2:DR19 DV2:DY19 DZ2:DZ4 EB2:EB4 EG2:EG4 EJ2:EJ4 EN2:EN4 ES2:ES4 EV2:EV4 FB2:FF19 FI2:FI4 FL2:FL4 FP2:FP4 FY2:FY4 GA2:GA4 GF2:GF4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Ya,Tidak"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I15:I19 H2:H19" xr:uid="{00000000-0002-0000-0000-000002000000}">
@@ -5581,130 +6097,130 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS2:AS19" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"1 s.d &lt;10 tahun lalu,10 s.d &lt;15 tahun lalu,15 tahun lalu atau lebih"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ2:CJ19" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN2:CN19" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"Normal,Abnormal TBC,Abnormal non TBC"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CK2:CK19" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP2:CP19" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"Riwayat kontak serumah,Riwayat kontak erat,Tidak ada,Tidak diketahui"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CL2:CL19" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CQ2:CQ19" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"Bakteriologis,Klinis"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM2:CM19" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CR2:CR19" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"TCM,BTA,NPOC,Tidak dilakukan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CO2:CO19" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CU2:CU19" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"Suspek frambusia,Bukan frambusia,Tidak Ada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CP2:CP19 FB2:FF19" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CV2:CV19 GB2:GE19 GG2:GG19 GF5:GF19" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"Reaktif,Non Reaktif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CQ2:CQ19" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CX2:CX19" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>"Kusta,Bukan kusta,Meragukan,Tidak Ada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CR2:CR19" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY2:CY19" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"Kusta,Bukan kusta,Meragukan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CS2:CS19" xr:uid="{00000000-0002-0000-0000-00000D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DA2:DA19" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"Skabies,Bukan Skabies,Meragukan,Tidak Ada"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CT2:CT19" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DC2:DC19" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>"Tidak ada serumen impaksi,Ada serumen impaksi"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CU2:CU19" xr:uid="{00000000-0002-0000-0000-00000F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DD2:DD19" xr:uid="{00000000-0002-0000-0000-00000F000000}">
       <formula1>"Tidak ada infeksi telinga,Ada infeksi telinga"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CV2:CV19" xr:uid="{00000000-0002-0000-0000-000010000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DE2:DE19" xr:uid="{00000000-0002-0000-0000-000010000000}">
       <formula1>"Normal,Curiga gangguan pendengaran"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CW2:CW19" xr:uid="{00000000-0002-0000-0000-000011000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DF2:DF19" xr:uid="{00000000-0002-0000-0000-000011000000}">
       <formula1>"Normal,Gangguan Pendengaran"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CX2:CX19" xr:uid="{00000000-0002-0000-0000-000012000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DG2:DG19" xr:uid="{00000000-0002-0000-0000-000012000000}">
       <formula1>"Normal (visus 6/6 - 6/12),Curiga gangguan penglihatan (visus &lt;6/12)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY2:CY19" xr:uid="{00000000-0002-0000-0000-000013000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DH2:DH19" xr:uid="{00000000-0002-0000-0000-000013000000}">
       <formula1>"Normal (visus 6/6 - 6/12),Gangguan penglihatan ringan (visus &lt;6/12 - 6/18),Gangguan penglihatan sedang (&lt;6/18 - 6/60),Gangguan penglihatan berat (&lt;6/60 - 3/60),Buta (&lt;3/60)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CZ2:CZ19" xr:uid="{00000000-0002-0000-0000-000014000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DI2:DI19" xr:uid="{00000000-0002-0000-0000-000014000000}">
       <formula1>"Visus membaik,Visus tidak membaik (visus tetap)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DA2:DA19" xr:uid="{00000000-0002-0000-0000-000015000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DJ2:DJ19" xr:uid="{00000000-0002-0000-0000-000015000000}">
       <formula1>"Kelainan refraksi ringan (0.50 - 3.00 Dioptri),Kelainan refraksi sedang (3.00 - 6.00 Dioptri),Kelainan refraksi berat (&gt;6.00 Dioptri)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DB2:DB19" xr:uid="{00000000-0002-0000-0000-000016000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DK2:DK19" xr:uid="{00000000-0002-0000-0000-000016000000}">
       <formula1>"Normal,Curiga kelainan mata"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DC2:DC19" xr:uid="{00000000-0002-0000-0000-000017000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DL2:DL19" xr:uid="{00000000-0002-0000-0000-000017000000}">
       <formula1>"Curiga katarak,Normal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DH2:DH19" xr:uid="{00000000-0002-0000-0000-000018000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DT2:DT19" xr:uid="{00000000-0002-0000-0000-000018000000}">
       <formula1>"Iya,Tidak"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DI2:DI19" xr:uid="{00000000-0002-0000-0000-000019000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DU2:DU19" xr:uid="{00000000-0002-0000-0000-000019000000}">
       <formula1>"&lt;20 bungkus per tahun,20-30 bungkus per tahun,&gt;30 bungkus per tahun"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DU2:DU19" xr:uid="{00000000-0002-0000-0000-00001A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EK2:EK19" xr:uid="{00000000-0002-0000-0000-00001A000000}">
       <formula1>"HBsAg Non Reaktif,HBsAg Reaktif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DV2:DV19" xr:uid="{00000000-0002-0000-0000-00001B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EL2:EL19" xr:uid="{00000000-0002-0000-0000-00001B000000}">
       <formula1>"Anti HCV Non Reaktif,Anti HCV Reaktif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DW2:DW19" xr:uid="{00000000-0002-0000-0000-00001C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EM2:EM19" xr:uid="{00000000-0002-0000-0000-00001C000000}">
       <formula1>"VL HCV RNA Negatif,VL HCV RNA Positif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EN2:EN19" xr:uid="{00000000-0002-0000-0000-00001D000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FJ2:FJ19" xr:uid="{00000000-0002-0000-0000-00001D000000}">
       <formula1>"Normal,Abnormal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EO2:EO19" xr:uid="{00000000-0002-0000-0000-00001E000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FK2:FK19" xr:uid="{00000000-0002-0000-0000-00001E000000}">
       <formula1>"Normal,Abnormal ST Depresi,Abnormal T Inversi,Abnormal Hipertrofi Ventrikel Kiri,Abnormal Atrial Fibrilasi,Abnormal Q-Patologis,Abnormal ST Elevasi,Abnormal Gambaran Abnormal Lainnya"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP2:EP19" xr:uid="{00000000-0002-0000-0000-00001F000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FM2:FM19" xr:uid="{00000000-0002-0000-0000-00001F000000}">
       <formula1>"Bersedia,Menolak,Tidak tahu"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EQ2:EQ19" xr:uid="{00000000-0002-0000-0000-000020000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FN2:FN19" xr:uid="{00000000-0002-0000-0000-000020000000}">
       <formula1>"Ditemukan benjolan,Tidak ditemukan benjolan"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EM2:EM19 ER2:ER19" xr:uid="{00000000-0002-0000-0000-000021000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FH2:FH19 FO2:FO19" xr:uid="{00000000-0002-0000-0000-000021000000}">
       <formula1>"Negatif,Positif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ES2:ES19" xr:uid="{00000000-0002-0000-0000-000022000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FQ2:FQ19" xr:uid="{00000000-0002-0000-0000-000022000000}">
       <formula1>"Memiliki diagnosis kanker &gt;5 tahun yang lalu,Memiliki diagnosis kanker &lt;5 tahun yang lalu,Tidak pernah didiagnosis menderita kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ET2:ET19" xr:uid="{00000000-0002-0000-0000-000023000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FR2:FR19" xr:uid="{00000000-0002-0000-0000-000023000000}">
       <formula1>"Memiliki keluarga yang terdiagnosis kanker paru,Memiliki keluarga yang terdiagnosis kanker lain,Tidak ada keluarga yang terdiagnosis kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EU2:EU19" xr:uid="{00000000-0002-0000-0000-000024000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FS2:FS19" xr:uid="{00000000-0002-0000-0000-000024000000}">
       <formula1>"Perokok aktif (dalam 1 tahun ini masih merokok),Perokok/bekas perokok berhenti &lt;10 tahun lalu,Perokok pasif dari lingkungan rumah/tempat kerja,Tidak pernah merokok"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EW2:EW19" xr:uid="{00000000-0002-0000-0000-000025000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FU2:FU19" xr:uid="{00000000-0002-0000-0000-000025000000}">
       <formula1>"Memiliki tempat tinggal berpotensi tinggi,Tidak yakin memiliki tempat tinggal berpotensi tinggi,Tidak memiliki tempat tinggal berpotensi tinggi"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EX2:EX19" xr:uid="{00000000-0002-0000-0000-000026000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FV2:FV19" xr:uid="{00000000-0002-0000-0000-000026000000}">
       <formula1>"Memiliki lingkungan dalam rumah yang tidak sehat,Tidak yakin memiliki lingkungan dalam rumah yang tidak sehat,Memiliki lingkungan dalam rumah yang sehat"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EZ2:EZ19" xr:uid="{00000000-0002-0000-0000-000027000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FX2:FX19 FY5:FY19" xr:uid="{00000000-0002-0000-0000-000027000000}">
       <formula1>"Normal,Tidak Normal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="ED2:ED19" xr:uid="{00000000-0002-0000-0000-000028000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EW2:EW19" xr:uid="{00000000-0002-0000-0000-000028000000}">
       <formula1>"SADANIS,USG Payudara"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EE2:EE19" xr:uid="{00000000-0002-0000-0000-000029000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EX2:EX19" xr:uid="{00000000-0002-0000-0000-000029000000}">
       <formula1>"Normal,Ditemukan benjolan,Curiga kanker"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EF2:EF19" xr:uid="{00000000-0002-0000-0000-00002A000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EY2:EY19 EZ5:EZ19" xr:uid="{00000000-0002-0000-0000-00002A000000}">
       <formula1>" Normal,Simple cyst,Non simple cyst"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EG2:EG19" xr:uid="{00000000-0002-0000-0000-00002B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FA2:FA19" xr:uid="{00000000-0002-0000-0000-00002B000000}">
       <formula1>"HPV Negatif,HPV Positif"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EL2:EL19" xr:uid="{00000000-0002-0000-0000-00002C000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FG2:FG19" xr:uid="{00000000-0002-0000-0000-00002C000000}">
       <formula1>"Normal,Curiga kanker"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AV15:AV19 AU2:AU19" xr:uid="{00000000-0002-0000-0000-00002D000000}">
       <formula1>"Pernah imunisasi tetanus minimal dua kali,Pernah imunisasi tetanus satu kali,Pernah imunisasi tetanus tetapi tidak ingat berapa kali,Tidak tahu atau tidak ingat"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N15:N19 M2:M19 AN2:AN19 CD2:CD19 CN2:CN19 EV2:EV19 EY2:EY19" xr:uid="{00000000-0002-0000-0000-00002E000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N15:N19 M2:M19 AN2:AN19 CH2:CH19 FW2:FW19 FT2:FT19 CS2:CS19" xr:uid="{00000000-0002-0000-0000-00002E000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
